--- a/data/分群結果.xlsx
+++ b/data/分群結果.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C155"/>
+  <dimension ref="A1:C162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,7 +435,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -495,22 +495,22 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>若有兩家或以上未蓋牌則攤牌比大小，依勝負分配總彩金。結束本回合，莊家位置依順時鐘次序移動至下一家進行下一輪。</t>
+          <t>若有兩家或以上未蓋牌則攤牌比大小，依勝負分配總彩金。結束本回合，莊家位置依順時針次序移動至下一家進行下一輪。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>若有 兩家 或 以上 未蓋 牌則 攤牌 比 大小 依勝負 分配 總彩金 結束 本 回合 莊家 位置 依順 時鐘 次序 移動 至 下 一家 進行 下 一輪</t>
+          <t>若有 兩家 或 以上 未蓋 牌則 攤牌 比 大小 依勝負 分配 總彩金 結束 本 回合 莊家 位置 依 順時針 次序 移動 至 下 一家 進行 下 一輪</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -519,22 +519,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>座位 分配 方式 發牌 次序 一般 撲克錦標賽 座位 均 採取 隨機 分配 私人 遊戲 多 抽牌 比 大小 決定 起始 座位 順序 及 第一 個 發牌者 位置 抽牌 選位 方法 每人 發一 張牌 抽到 最大 牌者 莊位 button 同 大小 則比 花色 每一輪 結束 後 莊家 依 順時針 方向 玩家 依序 輪流</t>
+          <t>座位 分配 方式 發牌 次序 一般 撲克錦標賽 座位 均 採取 隨機 分配 私人 遊戲 多 抽牌 比 大小 決定 起始 座位 順序 及 第一 個 發牌者 位置 抽牌 選位 方法 每人 發一 張牌 抽到 最大 牌者 莊位 button 同 大小 則比 花色 每一輪 結束 後 莊家 依 順時針 玩家 依序 輪流</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>下盲注（blinds）及切牌後進行發牌。在三人桌(含)以上皆由莊位（dealer_button）位置的下家(小盲注，small_blind)開始，依順時鐘方向派發，每輪一張共兩輪。每一個參加的玩家都會得到兩張底牌。</t>
+          <t>下盲注（blinds）及切牌後進行發牌。在三人桌(含)以上皆由莊位（dealer_button）位置的下家(小盲注，small_blind)開始，依順時針方向派發，每輪一張共兩輪。每一個參加的玩家都會得到兩張底牌。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>下 盲注 blinds 及 切牌 後 進行 發牌 三人桌 含 以上 皆 莊位 dealer_button 位置 下家 小盲注 small_blind 開始 依順 時鐘 方向 派發 每輪 一張 共 兩輪 每一個 參加 玩家 會 得到 兩張 底牌</t>
+          <t>下 盲注 blinds 及 切牌 後 進行 發牌 三人桌 含 以上 皆 莊位 dealer_button 位置 下家 小盲注 small_blind 開始 依 順時針 派發 每輪 一張 共 兩輪 每一個 參加 玩家 得到 兩張 底牌</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -579,13 +579,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>標準 德州撲克 遊戲 盲注 位置 小盲注 大盲注 緊接 發牌者 之 後 坐在 發牌 人 dealer 位置 玩家 前面 有 按鈕 button 作標示 位 發牌 人 順時針 方向 次 一 位置 玩家 須下 小盲注 small_blind 金額 等於 大盲注 big_blind 一半 小盲注 玩家 下 一家 玩家 須下 大盲注 金額 等於 最低 下注 額 每局 順時針 方向 輪流</t>
+          <t>標準 德州撲克 遊戲 盲注 位置 小盲注 大盲注 緊接 發牌者 之 後 坐在 發牌 人 dealer 位置 玩家 前面 有 按鈕 button 作標示 位 發牌 人 順時針 次 一 位置 玩家 須下 小盲注 small_blind 金額 等於 大盲注 big_blind 一半 小盲注 玩家 下 一家 玩家 須下 大盲注 金額 等於 最低 下注 額 每局 順時針 輪流</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>如 只 剩 兩名 玩家 一對 一 heads_up 特別 規則 會 生效 這個 情況 下 莊位 下 小盲注 他 對手 須下 大盲注 第一 輪 莊位 先 叫注 翻牌後 各輪 皆 大盲注 先行 叫注</t>
+          <t>如 只 剩 兩名 玩家 一對 一 heads_up 特別 規則 生效 這個 情況 下 莊位 下 小盲注 他 對手 須下 大盲注 第一 輪 莊位 先 叫注 翻牌後 各輪 皆 大盲注 先行 叫注</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -744,13 +744,13 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>攤牌 平手 次大牌 kicker 規則 如多 一名 玩家 擁有 最大 手牌 彩池 他們 平等 均分 不能 平分 零頭 發牌者 順時針 方向 尚未 蓋牌 第一 個 玩家 獲得 玩家 牌型 大小 相若 須以 次大牌 kicker 決定 勝負 次大牌 相同 則 依序 比 到 使用 五張 為止 攤牌 時 只 計算 數字 大小 花色 德州撲克 中無分 大小</t>
+          <t>攤牌 平手 次大牌 kicker 規則 如多 一名 玩家 擁有 最大 手牌 彩池 他們 平等 均分 不能 平分 零頭 發牌者 順時針 尚未 蓋牌 第一 個 玩家 獲得 玩家 牌型 大小 相若 須以 次大牌 kicker 決定 勝負 次大牌 相同 則 依序 比 到 使用 五張 為止 攤牌 時 只 計算 數字 大小 花色 德州撲克 中無分 大小</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -810,22 +810,22 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>彩池無法均分時的小額籌碼分配：當彩池由兩個以上玩家平分時，若有無法平分之小額籌碼（零頭），將由順時鐘方向算過去，最靠近發牌者(Dealer)的贏家取得。</t>
+          <t>彩池無法均分時的小額籌碼分配：當彩池由兩個以上玩家平分時，若有無法平分之小額籌碼（零頭），將由順時針方向算過去，最靠近發牌者(Dealer)的贏家取得。</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>彩池 無法 均分 時 小額 籌碼 分配 當彩池 兩個 以上 玩家 平分 時 若有 無法 平分 之小額 籌碼 零頭 將由順 時鐘 方向 算過 去 最靠近 發牌者 dealer 贏家 取得</t>
+          <t>彩池 無法 均分 時 小額 籌碼 分配 當彩池 兩個 以上 玩家 平分 時 若有 無法 平分 之小額 籌碼 零頭 將由 順時針 算過 去 最靠近 發牌者 dealer 贏家 取得</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -999,13 +999,13 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>德州撲克 位置 策略 位置 往往 比牌力 更 關鍵 行動 越晚 資訊越 多 sb bb 盲注位 翻牌後 最先 行動 資訊 最少 應打 得 更 保守 utg mp 前中位 起手 牌範圍 要 嚴格 避免 邊緣牌 co btn 後位 可以 主動 偷盲 控制 底池 同一 手牌 後位 賺 錢牌 前位 可能 陷阱</t>
+          <t>德州撲克 位置 策略 位置 往往 比牌力 更 關鍵 行動 越晚 資訊越 多 sb bb 盲注位 翻牌後 最先 行動 資訊 最少 應打 得 更 保守 utg mp 前中位 起手牌 範圍 要 嚴格 避免 邊緣牌 co btn 後位 可以 主動 偷盲 控制 底池 同一 手牌 後位 賺 錢牌 前位 可能 陷阱</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1024,18 +1024,18 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>outs，有一或多張牌可以把你的牌型變成一手贏牌的牌型</t>
+          <t>outs，補牌，有一或多張牌可以把你的牌型變成一手贏牌的牌型</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>outs 有 一 或 多 張牌 可以 把 你 牌型 變成 一手 贏牌 牌型</t>
+          <t>outs 補牌 有 一 或 多 張牌 可以 你 牌型 變成 一手 贏牌 牌型</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1050,61 +1050,61 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>底池賠率（pot_odds）是德州撲克中評估投資報酬率的重要數學指標。它的核心概念是比較玩家「必須跟注的成本」與「最終可能贏得的總獎金」之間的比例，藉此衡量跟注是否划算。</t>
+          <t>底池賠率計算：底池總額除以跟注需要的金額除以一</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>底池 賠率 pot_odds 德州撲克 中 評估 投資 報酬 率 重要 數學 指標 它 核心 概念 比 較 玩家 必須 跟注 成本 最終 可能 贏得 總獎 金 之間 比例 藉此 衡量 跟注 是否 划算</t>
+          <t>底池賠率 計算 底池總額 除以 跟注 需要 金額 除以 一</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>在進行跟注決策時，玩家應比較聽牌成功率與底池賠率。當估算出的勝率優於賠率時，代表這個跟注動作長期下來具有正向的期望值，屬於能穩定獲利的有利決策。</t>
+          <t>底池賠率（pot_odds）是德州撲克中評估投資報酬率的重要數學指標。我們需要跟注的籌碼與底池中的籌碼比例。它的核心概念是比較玩家「必須跟注的成本」與「最終可能贏得的總獎金」之間的比例，藉此衡量跟注是否划算。能絕對有效地幫助我們判斷手牌。</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>進行 跟注 決策 時 玩家 應比較 聽牌 成功率 底池 賠率 當 估算 出 勝率 優 賠率 時 代表 這個 跟注 動作長 期下 來 具有 正向 期望值 屬於能 穩定 獲利 有利 決策</t>
+          <t>底池賠率 pot_odds 德州撲克 中 評估 投資 報酬 率 重要 數學 指標 我們 需要 跟注 籌碼 底池 中 籌碼 比例 它 核心 概念 比 較 玩家 必須 跟注 成本 最終 可能 贏得 總獎 金 之間 比例 藉此 衡量 跟注 是否 划算 能絕 有效 地幫助 我們 判斷 手牌</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>常見聽牌機率與賠率：同花聽牌（flush_draw）有9張outs，翻牌到河牌成功率相對高，賠率約1.9比1。開口順子聽牌（OESD）有8張outs，成功率相對高，賠率約2.1比1。內聽順子（Gutshot）有4張outs，成功率約中等，賠率約5比1。</t>
+          <t>在進行跟注決策時，玩家應比較聽牌成功率與底池賠率。當估算出的勝率優於賠率時，代表這個跟注動作長期下來具有正向的期望值，屬於能穩定獲利的有利決策。</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>常見 聽牌 機率 賠率 同花 聽牌 flush_draw 有 9 張 outs 翻牌 到 河牌 成功率 相對 高 賠率 約 1.9 比 1 開口 順子 聽牌 oesd 有 8 張 outs 成功率 相對 高 賠率 約 2.1 比 1 內 聽 順子 gutshot 有 4 張 outs 成功率 約 中等 賠率 約 5 比 1</t>
+          <t>進行 跟注 決策 時 玩家 應比較 聽牌 成功率 底池賠率 估算 出 勝率 優 賠率 時 代表 這個 跟注 動作長 期下 來 具有 正向 期望值 屬於能 穩定 獲利 有利 決策</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>遊戲人數與牌局組成：德州撲克一般支援 2 到 10 名玩家，現金局（cash_game）通常以 6 到 9 人最為普遍。遊戲中每位玩家會獲發 2 張隱藏的「手牌（hole_cards）」。桌面會發出 5 張所有人共用的「公共牌（Community_cards）」，分為前三張的「翻牌（Flop）」、第四張的「轉牌（Turn）」與第五張的「河牌（River）」。</t>
+          <t>常見聽牌機率與賠率：同花聽牌（flush_draw）有9張outs，翻牌到河牌成功率相對高，賠率約1.9比1。開口順子聽牌（OESD）有8張outs，成功率相對高，賠率約2.1比1。內聽順子（Gutshot）有4張outs，成功率約中等，賠率約5比1。</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>遊戲 人數 牌局 組成 德州撲克 一般 支援 2 到 10 名 玩家 現金局 cash_game 通常 6 到 9 人 最 普遍 遊戲 中 每位 玩家 會 獲發 2 張隱藏 手牌 hole_cards 桌面 會 發出 5 張 所有人 共用 公共牌 community_cards 分為 前三張 翻牌 flop 第四 張 轉牌 turn 第五 張 河牌 river</t>
+          <t>常見 聽牌 機率 賠率 同花 聽牌 flush_draw 有 9 張 outs 翻牌 到 河牌 成功率 相對 高 賠率 約 1.9 比 1 開口 順子 聽牌 oesd 有 8 張 outs 成功率 相對 高 賠率 約 2.1 比 1 內 聽 順子 gutshot 有 4 張 outs 成功率 約 中等 賠率 約 5 比 1</t>
         </is>
       </c>
     </row>
@@ -1114,42 +1114,42 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>最佳五張牌組合與打公牌（Play_the_board）：玩家需從手裡的 2 張手牌，加上桌面的 5 張公共牌，共 7 張牌中選出任意 5 張，做出最大的牌型組合。這 5 張牌可以是手裡 2 張加桌面 3 張，或是手裡 1 張加桌面 4 張；若桌面 5 張公共牌已是最大組合，也可以完全不使用手牌，稱為「打公牌（Play_the_board）」。</t>
+          <t>遊戲人數與牌局組成：德州撲克一般支援 2 到 10 名玩家，現金局（cash_game）通常以 6 到 9 人最為普遍。遊戲中每位玩家會獲發 2 張隱藏的「手牌（hole_cards）」。桌面會發出 5 張所有人共用的「公共牌（Community_cards）」，分為前三張的「翻牌（Flop）」、第四張的「轉牌（Turn）」與第五張的「河牌（River）」。</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>最佳 五張牌 組合 打 公牌 play_the_board 玩家 需從 手裡 2 張手牌 加上 桌面 5 張 公共牌 共 7 張牌 中選出 任意 5 張 做出 最大 牌型 組合 這 5 張牌 可以 手裡 2 張加 桌面 3 張 或是 手裡 1 張加 桌面 4 張 桌面 5 張 公共牌 已 最大 組合 可以 完全 不 使用 手牌 稱為 打 公牌 play_the_board</t>
+          <t>遊戲 人數 牌局 組成 德州撲克 一般 支援 2 到 10 名 玩家 現金局 cash_game 通常 6 到 9 人 最 普遍 遊戲 中 每位 玩家 獲發 2 張隱藏 手牌 hole_cards 桌面 發出 5 張 所有人 共用 公共牌 community_cards 分為 前三張 翻牌 flop 第四 張 轉牌 turn 第五 張 河牌 river</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>盲注與發牌順序：發牌前，小盲位（small_blind, SB）與大盲位（Big_Blind, BB）玩家必須強制支付盲注籌碼。發牌時由小盲位開始，接著是大盲、槍口位（Under_the_Gun, UTG），依順時針方向輪流，最後發給莊家按鈕位（Button）。每位玩家共會獲發兩張手牌。</t>
+          <t>最佳五張牌組合與打公牌（Play_the_board）：玩家需從手裡的 2 張手牌，加上桌面的 5 張公共牌，共 7 張牌中選出任意 5 張，做出最大的牌型組合。這 5 張牌可以是手裡 2 張加桌面 3 張，或是手裡 1 張加桌面 4 張；若桌面 5 張公共牌已是最大組合，也可以完全不使用手牌，稱為「打公牌（Play_the_board）」。</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>盲注 發牌 順序 發牌 前 小盲位 small_blind , sb 大盲位 big_blind , bb 玩家 必須 強制 支付 盲注 籌碼 發牌 時 小盲位 開始 接著 大盲 槍口位 under_the_gun , utg 依 順時針 方向 輪流 最後發給 莊家 按鈕位 button 每位 玩家 共會 獲發 兩張 手牌</t>
+          <t>最佳 五張牌 組合 打 公牌 play_the_board 玩家 需從 手裡 2 張手牌 加上 桌面 5 張 公共牌 共 7 張牌 中選出 任意 5 張 做出 最大 牌型 組合 5 張牌 可以 手裡 2 張加 桌面 3 張 或是 手裡 1 張加 桌面 4 張 桌面 5 張 公共牌 已 最大 組合 可以 完全 不 使用 手牌 稱為 打 公牌 play_the_board</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>翻牌前後行動順序與選項：翻牌前（Pre_flop）因為盲注已下注，由大盲注左側的槍口位（UTG）第一個行動，可選擇棄牌（Fold）、跟注（Call）或加注（Raise）。翻牌後（Post_flop）則由小盲位開始行動；若該下注圈尚未有人下注，玩家多出「過牌（Check）」的選擇。若前方已經有人下注或加注，則後方玩家不能選擇過牌。</t>
+          <t>盲注與發牌順序：發牌前，小盲位（small_blind, SB）與大盲位（Big_Blind, BB）玩家必須強制支付盲注籌碼。發牌時由小盲位開始，接著是大盲、槍口位（Under_the_Gun, UTG），依順時針方向輪流，最後發給莊家按鈕位（Button）。每位玩家共會獲發兩張手牌。</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>翻牌前 後 行動 順序 選項 翻牌前 pre_flop 因為 盲注 已 下注 大盲注 左側 槍口位 utg 第一 個 行動 可選擇 棄牌 fold 跟注 call 或 加注 raise 翻牌後 post_flop 則由 小盲位 開始 行動 若該 下注圈 尚未 有人 下注 玩家 多出 過牌 check 選擇 前方 已經 有人 下注 或 加注 則後方 玩家 不能 選擇 過牌</t>
+          <t>盲注 發牌 順序 發牌 前 小盲位 small_blind , sb 大盲位 big_blind , bb 玩家 必須 強制 支付 盲注 籌碼 發牌 時 小盲位 開始 接著 大盲 槍口位 under_the_gun , utg 依 順時針 輪流 最後發給 莊家 按鈕位 button 每位 玩家 共會 獲發 兩張 手牌</t>
         </is>
       </c>
     </row>
@@ -1159,147 +1159,147 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>下注圈結束的標誌：每一輪下注（Betting_round）結束的標誌是，所有決定繼續參與該局的玩家，最終都投入了一樣多的籌碼於彩池中。如果玩家不想再投入與其他人同等的籌碼，就必須選擇棄牌（Fold）。</t>
+          <t>翻牌前後行動順序與選項：翻牌前（Pre_flop）因為盲注已下注，由大盲注左側的槍口位（UTG）第一個行動，可選擇棄牌（Fold）、跟注（Call）或加注（Raise）。翻牌後（Post_flop）則由小盲位開始行動；若該下注圈尚未有人下注，玩家多出「過牌（Check）」的選擇。若前方已經有人下注或加注，則後方玩家不能選擇過牌。</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>下注圈 結束 標誌 每一輪 下注 betting_round 結束 標誌 所有 決定 繼續 參與 該局 玩家 最終 投入 一樣 多 籌碼 彩池 中 如果 玩家 不想 再 投入 其他人 同等 籌碼 必須 選擇 棄牌 fold</t>
+          <t>翻牌前 後 行動 順序 選項 翻牌前 pre_flop 因為 盲注 已 下注 大盲注 左側 槍口位 utg 第一 個 行動 可選擇 棄牌 fold 跟注 call 或 加注 raise 翻牌後 post_flop 則由 小盲位 開始 行動 若該 下注圈 尚未 有人 下注 玩家 多出 過牌 check 選擇 前方 已經 有人 下注 或 加注 則後方 玩家 不能 選擇 過牌</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>銷牌（Burn_card）規則：在發出任何公共牌（翻牌、轉牌、河牌）之前，發牌員都必須先「銷牌（Burn）」，即捨棄牌堆頂端的第一張牌（不予使用）。銷牌後才發出公共牌（翻牌發 3 張，轉牌與河牌各發 1 張），此機制的目的是為了防止作弊或作號。</t>
+          <t>下注圈結束的標誌：每一輪下注（Betting_round）結束的標誌是，所有決定繼續參與該局的玩家，最終都投入了一樣多的籌碼於彩池中。如果玩家不想再投入與其他人同等的籌碼，就必須選擇棄牌（Fold）。</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>銷牌 burn_card 規則 發出 任何 公共牌 翻牌 轉牌 河牌 之前 發牌 員 必須 先 銷牌 burn 即 捨 棄牌 堆頂 端的 第一 張牌 不予 使用 銷牌 後 才 發出 公共牌 翻牌 發 3 張 轉牌 河牌 各發 1 張 此機制 目的 防止 作弊 或 作號</t>
+          <t>下注圈 結束 標誌 每一輪 下注 betting_round 結束 標誌 所有 決定 繼續 參與 該局 玩家 最終 投入 一樣 多 籌碼 彩池 中 如果 玩家 不想 再 投入 其他人 同等 籌碼 必須 選擇 棄牌 fold</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>翻牌後行動順序與棄牌遞延：翻牌後的各個下注圈，標準順序是由小盲位開始順時針行動，按鈕位（Button）通常是最後一個行動的優勢位置。若前方的盲注位玩家已棄牌，則由按鈕位左側「剩下未棄牌的第一位玩家」開始行動。</t>
+          <t>銷牌（Burn_card）規則：在發出任何公共牌（翻牌、轉牌、河牌）之前，發牌員都必須先「銷牌（Burn）」，即捨棄牌堆頂端的第一張牌（不予使用）。銷牌後才發出公共牌（翻牌發 3 張，轉牌與河牌各發 1 張），此機制的目的是為了防止作弊或作號。</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>翻牌後 行動 順序 棄牌 遞延 翻牌後 各個 下注圈 標準 順序 小盲位 開始 順時針 行動 按鈕位 button 通常 最後一個 行動 優勢 位置 前方 盲注位 玩家 已 棄牌 則由 按鈕位 左側 剩下 未 棄牌 第一位 玩家 開始 行動</t>
+          <t>銷牌 burn_card 規則 發出 任何 公共牌 翻牌 轉牌 河牌 之前 發牌 員 必須 先 銷牌 burn 即 捨 棄牌 堆頂 端的 第一 張牌 不予 使用 銷牌 後 才 發出 公共牌 翻牌 發 3 張 轉牌 河牌 各發 1 張 此機制 目的 防止 作弊 或 作號</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>攤牌與下注逼退（Bluffing 概念）：在最後一圈行動中，若所有玩家皆選擇過牌（Check）或跟注至金額相同，則進入攤牌（Showdown）比大小。若玩家不想攤牌比牌力，可以選擇下注或加注更多的籌碼，利用下注壓力迫使跟不下的對手棄牌（Fold），藉此直接贏得底池。</t>
+          <t>翻牌後行動順序與棄牌遞延：翻牌後的各個下注圈，標準順序是由小盲位開始順時針行動，按鈕位（Button）通常是最後一個行動的優勢位置。若前方的盲注位玩家已棄牌，則由按鈕位左側「剩下未棄牌的第一位玩家」開始行動。</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>攤牌 下注 逼退 bluffing 概念 最 後 一圈 行動 中 所有 玩家 皆 選擇 過牌 check 或 跟注 至金額 相同 則進入 攤牌 showdown 比 大小 玩家 不想 攤牌 比牌力 可以 選擇 下注 或 加注 更 多 籌碼 利用 下注 壓力 迫使 跟 不下 對手 棄牌 fold 藉此 直接 贏得 底池</t>
+          <t>翻牌後 行動 順序 棄牌 遞延 翻牌後 各個 下注圈 標準 順序 小盲位 開始 順時針 行動 按鈕位 button 通常 最後一個 行動 優勢 位置 前方 盲注位 玩家 已 棄牌 則由 按鈕位 左側 剩下 未 棄牌 第一位 玩家 開始 行動</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>新加入牌桌的觀察策略與玩家分類：加入新牌桌時不應急於入局，應優先觀察對手打法。特別是透過對手攤牌（Showdown）時秀出的底牌，回溯其下注邏輯。這有助於快速將玩家分類，辨識出高手、激進型玩家、保守型玩家、喜歡詐唬（Bluff）的玩家，以及情緒失控（上頭 / Tilt）的玩家。</t>
+          <t>攤牌與下注逼退（Bluffing 概念）：在最後一圈行動中，若所有玩家皆選擇過牌（Check）或跟注至金額相同，則進入攤牌（Showdown）比大小。若玩家不想攤牌比牌力，可以選擇下注或加注更多的籌碼，利用下注壓力迫使跟不下的對手棄牌（Fold），藉此直接贏得底池。</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>新 加入 牌桌 觀察 策略 玩家 分類 加入 新 牌桌 時不應 急 入局 應 優先 觀察 對手 打法 特別 透過 對手 攤牌 showdown 時秀出 底牌 回溯 其 下注 邏輯 這 有助 快速 將 玩家 分類 辨識出 高手 激進型 玩家 保守 型 玩家 喜歡 詐唬 bluff 玩家 情緒 失控 上頭 tilt 玩家</t>
+          <t>攤牌 下注 逼退 bluffing 概念 最 後 一圈 行動 中 所有 玩家 皆 選擇 過牌 check 或 跟注 至金額 相同 則進入 攤牌 showdown 比 大小 玩家 不想 攤牌 比牌力 可以 選擇 下注 或 加注 更 多 籌碼 利用 下注 壓力 迫使 跟 不下 對手 棄牌 fold 藉此 直接 贏得 底池</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>翻牌前的看牌時機與肢體語言（Tells）：翻牌前（Pre_flop）不應一拿到手牌就立刻查看，以免下意識的表情或肢體動作洩漏自身的牌力意圖給對手。正確的做法是先觀察其他玩家看牌時的反應來搜集資訊，直到輪到自己行動時才查看底牌，以確保透露給對手的資訊降至最低。</t>
+          <t>新加入牌桌的觀察策略與玩家分類：加入新牌桌時不應急於入局，應優先觀察對手打法。特別是透過對手攤牌（Showdown）時秀出的底牌，回溯其下注邏輯。這有助於快速將玩家分類，辨識出高手、激進型玩家、保守型玩家、喜歡詐唬（Bluff）的玩家，以及情緒失控（上頭 / Tilt）的玩家。</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>翻牌前 看牌 時機 肢體 語言 tells 翻牌前 pre_flop 不應 一 拿到 手牌 立刻 查看 以免 下意識 表情 或肢 體動作 洩漏 自身 牌力意 圖給 對手 正確 做法 先 觀察 其他 玩家 看牌 時 反應 來 搜集 資訊 直到 自己 行動 時才 查看 底牌 以確 保 透露 給 對手 資訊降 至 最低</t>
+          <t>新 加入 牌桌 觀察 策略 玩家 分類 加入 新 牌桌 時不應 急 入局 應 優先 觀察 對手 打法 特別 透過 對手 攤牌 showdown 時秀出 底牌 回溯 其 下注 邏輯 有助 快速 將 玩家 分類 辨識出 高手 激進型 玩家 保守 型 玩家 喜歡 詐唬 bluff 玩家 情緒 失控 上頭 tilt 玩家</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>坐下：您可以在賭場的空位中自由選擇座位，但是在德州撲克中與座位是一個非常重要的因素，因此在賽事或與牌友玩時通常，座位的順序由規定好的座位表或撲克牌確定。</t>
+          <t>翻牌前的看牌時機與肢體語言（Tells）：翻牌前（Pre_flop）不應一拿到手牌就立刻查看，以免下意識的表情或肢體動作洩漏自身的牌力意圖給對手。正確的做法是先觀察其他玩家看牌時的反應來搜集資訊，直到輪到自己行動時才查看底牌，以確保透露給對手的資訊降至最低。</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>坐下 您 可以 賭場 空位 中 自由 選擇 座位 但是 德州撲克 中 座位 非常 重要 因素 因此 賽事 或 牌友 玩時 通常 座位 順序 規定 好 座位表 或 撲克牌 確定</t>
+          <t>翻牌前 看牌 時機 肢體 語言 tells 翻牌前 pre_flop 不應 一 拿到 手牌 立刻 查看 以免 下意識 表情 或肢 體動作 洩漏 自身 牌力意 圖給 對手 正確 做法 先 觀察 其他 玩家 看牌 時 反應 來 搜集 資訊 直到 自己 行動 時才 查看 底牌 以確 保 透露 給 對手 資訊降 至 最低</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>荷官莊家位置的確定：座位決定之後，接下來決定荷官莊家位。第一個按鈕莊家的位置是荷官（發牌的人）將牌一張一張地分發給玩家，拿到最強牌的人確定為莊家位。 確定按鈕莊家位的玩家後，就開始正式發牌。</t>
+          <t>坐下：您可以在賭場的空位中自由選擇座位，但是在德州撲克中與座位是一個非常重要的因素，因此在賽事或與牌友玩時通常，座位的順序由規定好的座位表或撲克牌確定。</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>荷官 莊家 位置 確定 座位 決定 之 後 接下 來 決定 荷官 莊家 位 第一 個 按鈕 莊家 位置 荷官 發牌 人 將牌 一張 一張 地分 發給 玩家 拿到 最強 牌 人 確定 莊家 位 確定 按鈕 莊家 位 玩家 後 開始 正式 發牌</t>
+          <t>坐下 您 可以 賭場 空位 中 自由 選擇 座位 但是 德州撲克 中 座位 非常 重要 因素 因此 賽事 或 牌友 玩時 通常 座位 順序 規定 好 座位表 或 撲克牌 確定</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>發牌：每個玩家發到2張排面朝下的牌，游戲開始。 這2張牌稱為「底牌」或「口袋牌」。 游戲中只有2張牌是發給每位玩家的，除了進行攤牌外，沒有必要將它展示給其他玩家，並且必須 小心不要被人看到它。</t>
+          <t>荷官莊家位置的確定：座位決定之後，接下來決定荷官莊家位。第一個按鈕莊家的位置是荷官（發牌的人）將牌一張一張地分發給玩家，拿到最強牌的人確定為莊家位。 確定按鈕莊家位的玩家後，就開始正式發牌。</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>發牌 每個 玩家 發到 2 張排 面朝 下 牌 游戲 開始 這 2 張牌 稱 底牌 或 口袋 牌 游戲 中 只有 2 張牌 發給 每位 玩家 除了 進行 攤牌 外 沒有 必要 將它 展示 給 其他 玩家 並且 必須 小心 不要 人 看到 它</t>
+          <t>荷官 莊家 位置 確定 座位 決定 之 後 接下 來 決定 荷官 莊家 位 第一 個 按鈕 莊家 位置 荷官 發牌 人 將牌 一張 一張 地分 發給 玩家 拿到 最強 牌 人 確定 莊家 位 確定 按鈕 莊家 位 玩家 後 開始 正式 發牌</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>翻牌前：先下大小盲注，然後給每個玩家發2張底牌，大盲注後面第一個玩家選擇跟注、加注或者蓋牌放棄，按照順時針方向，其他玩家依次表態，大盲注玩家最後表態 ，如果玩家有加注情況，前面已經跟注的玩家需要再次表態甚至多次表態。</t>
+          <t>發牌：每個玩家發到2張排面朝下的牌，游戲開始。 這2張牌稱為「底牌」或「口袋牌」。 游戲中只有2張牌是發給每位玩家的，除了進行攤牌外，沒有必要將它展示給其他玩家，並且必須 小心不要被人看到它。</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>翻牌前 先下 大 小盲注 然後給 每個 玩家 發 2 張 底牌 大盲注 後 面 第一 個 玩家 選擇 跟注 加注 或者 蓋牌 放棄 按照 順時針 方向 其他 玩家 依次 表態 大盲注 玩家 最後表態 如果 玩家 有 加注 情況 前面 已經 跟注 玩家 需要 再次 表態 甚至 多次 表態</t>
+          <t>發牌 每個 玩家 發到 2 張排 面朝 下 牌 游戲 開始 2 張牌 稱 底牌 或 口袋 牌 游戲 中 只有 2 張牌 發給 每位 玩家 除了 進行 攤牌 外 沒有 必要 將它 展示 給 其他 玩家 並且 必須 小心 不要 人 看到 它</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 翻牌：同時發三張公牌，由小盲注開始（如果小盲注已蓋牌，由後面最近的玩家開始，以此類推），按照順時針方向依次表態，玩家可以選擇下注、加注、或者蓋牌放棄。</t>
+          <t>翻牌前：先下大小盲注，然後給每個玩家發2張底牌，大盲注後面第一個玩家選擇跟注、加注或者蓋牌放棄，按照順時針方向，其他玩家依次表態，大盲注玩家最後表態 ，如果玩家有加注情況，前面已經跟注的玩家需要再次表態甚至多次表態。</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>翻牌 同時 發三張 公牌 小盲注 開始 如果 小盲注 已蓋牌 由後面 最近 玩家 開始 以此 類推 按照 順時針 方向 依次 表態 玩家 可以 選擇 下注 加注 或者 蓋牌 放棄</t>
+          <t>翻牌前 先下 大 小盲注 然後給 每個 玩家 發 2 張 底牌 大盲注 後 面 第一 個 玩家 選擇 跟注 加注 或者 蓋牌 放棄 按照 順時針 其他 玩家 依次 表態 大盲注 玩家 最後表態 如果 玩家 有 加注 情況 前面 已經 跟注 玩家 需要 再次 表態 甚至 多次 表態</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 轉牌&amp;河牌：Turn—發第四張牌，由小盲注開始，按照順時針依次表態。 River—發第五張牌，由小盲注開始，按照順時針方向依次表態，玩家可以選擇下注、加注、或者蓋牌放棄。經過前面四輪發牌和下注，還剩餘2名以上的玩家時，開始比大小，這時候需要亮牌。</t>
+          <t xml:space="preserve"> 翻牌：同時發三張公牌，由小盲注開始（如果小盲注已蓋牌，由後面最近的玩家開始，以此類推），按照順時針方向依次表態，玩家可以選擇下注、加注、或者蓋牌放棄。</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>轉牌 &amp; 河牌 turn — 發 第四 張牌 小盲注 開始 按照 順時針 依次 表態 river — 發 第五 張牌 小盲注 開始 按照 順時針 方向 依次 表態 玩家 可以 選擇 下注 加注 或者 蓋牌 放棄 經過 前面 四輪 發牌 和 下注 還剩 餘 2 名 以上 玩家 時 開始 比 大小 這時候 需要 亮牌</t>
+          <t>翻牌 同時 發三張 公牌 小盲注 開始 如果 小盲注 已蓋牌 由後面 最近 玩家 開始 以此 類推 按照 順時針 依次 表態 玩家 可以 選擇 下注 加注 或者 蓋牌 放棄</t>
         </is>
       </c>
     </row>
@@ -1339,417 +1339,417 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>亮牌：剩餘2名以上的玩家開始亮牌比大小，成牌最大的玩家贏取池底。亮牌是用自己的2張底牌和5張公共牌結合在一起，選出5張牌，通過比大小決定勝者。不論手中的牌使用幾張（甚至可以不用手中的底牌），湊成最大的成牌，跟其他玩家比大小。</t>
+          <t xml:space="preserve"> 轉牌&amp;河牌：Turn—發第四張牌，由小盲注開始，按照順時針依次表態。 River—發第五張牌，由小盲注開始，按照順時針方向依次表態，玩家可以選擇下注、加注、或者蓋牌放棄。經過前面四輪發牌和下注，還剩餘2名以上的玩家時，開始比大小，這時候需要亮牌。</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>亮牌 剩餘 2 名 以上 玩家 開始 亮牌 比 大小 成牌 最大 玩家 贏取 池底 亮牌 用 自己 2 張 底牌 和 5 張 公共牌 結 合在一起 選出 5 張牌 通過 比 大小 決定 勝者 不論 手中 牌 使用 幾張 甚至 可以 不用 手中 底牌 湊成 最大 成牌 跟 其他 玩家 比 大小</t>
+          <t>轉牌 &amp; 河牌 turn — 發 第四 張牌 小盲注 開始 按照 順時針 依次 表態 river — 發 第五 張牌 小盲注 開始 按照 順時針 依次 表態 玩家 可以 選擇 下注 加注 或者 蓋牌 放棄 經過 前面 四輪 發牌 和 下注 還剩 餘 2 名 以上 玩家 時 開始 比 大小 需要 亮牌</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>叫注(也叫說話)：･讓牌 - 在無需跟進的情況下選擇把決定「讓」給下一位 ･押注 - 押上籌碼 ･棄牌 - 放棄繼續牌局的機會 ･加注 - 在其他玩家下注後，把現有的注金抬高 ･跟進 - 跟隨眾人押上同等的注額 ･全押 - 一次過把手上的籌碼全押上</t>
+          <t>亮牌：剩餘2名以上的玩家開始亮牌比大小，成牌最大的玩家贏取池底。亮牌是用自己的2張底牌和5張公共牌結合在一起，選出5張牌，通過比大小決定勝者。不論手中的牌使用幾張（甚至可以不用手中的底牌），湊成最大的成牌，跟其他玩家比大小。</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>叫注 叫 說 話 讓 牌 無 需 跟 進 情況 下 選擇 把 決定 讓 給下 一位 押注 押 上 籌碼 棄牌 放棄 繼續 牌局 機會 加注 其他 玩家 下注 後 把 現有 注金 抬高 跟 進 跟 隨眾 人 押 上 同等 注額 全押 一次 過把 手上 籌碼 全押 上</t>
+          <t>亮牌 剩餘 2 名 以上 玩家 開始 亮牌 比 大小 成牌 最大 玩家 贏取 池底 亮牌 用 自己 2 張 底牌 和 5 張 公共牌 結 合在一起 選出 5 張牌 通過 比 大小 決定 勝者 不論 手中 牌 使用 幾張 甚至 可以 不用 手中 底牌 湊成 最大 成牌 跟 其他 玩家 比 大小</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>高牌是指沒有湊成以上任何牌型的情況，只能比單張牌的大小，也是遊戲中相當常見的狀況。</t>
+          <t>叫注(也叫說話)：･讓牌 - 在無需跟進的情況下選擇把決定「讓」給下一位 ･押注 - 押上籌碼 ･棄牌 - 放棄繼續牌局的機會 ･加注 - 在其他玩家下注後，把現有的注金抬高 ･跟進 - 跟隨眾人押上同等的注額 ･全押 - 一次過把手上的籌碼全押上</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>高牌 沒 有 湊成 以上 任何 牌型 情況 只能 比單 張牌 大小 遊戲 中相 當常見 狀況</t>
+          <t>叫注 叫 說 話 讓 牌 無 需 跟 進 情況 下 選擇 決定 讓 給下 一位 押注 押 上 籌碼 棄牌 放棄 繼續 牌局 機會 加注 其他 玩家 下注 後 現有 注金 抬高 跟 進 跟 隨眾 人 押 上 同等 注額 全押 一次 過把 手上 籌碼 全押 上</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>一對是由兩張同一個數字的牌所組成，這是德州撲克中最常見的牌型，出現機率非常高。</t>
+          <t>高牌是指沒有湊成以上任何牌型的情況，只能比單張牌的大小，也是遊戲中相當常見的狀況。</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>一對 兩張 同一 個 數字 牌 所 組成 這是 德州撲克 中 最常見 牌型 出現 機率 非常 高</t>
+          <t>高牌 沒 有 湊成 以上 任何 牌型 情況 只能 比單 張牌 大小 遊戲 中相 當常見 狀況</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>兩對是由兩組不同數字的對子所組成，是遊戲中相當常見的牌型。</t>
+          <t>一對是由兩張同一個數字的牌所組成，這是德州撲克中最常見的牌型，出現機率非常高。</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>兩對 兩組 不同 數字 對子 所 組成 遊戲 中相 當常見 牌型</t>
+          <t>一對 兩張 同一 個 數字 牌 所 組成 這是 德州撲克 中 最常見 牌型 出現 機率 非常 高</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>三條是由三張同一個數字的牌所組成，出現的機率稍低。</t>
+          <t>兩對是由兩組不同數字的對子所組成，是遊戲中相當常見的牌型。</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>三條 三張 同一 個 數字 牌 所 組成 出現 機率 稍低</t>
+          <t>兩對 兩組 不同 數字 對子 所 組成 遊戲 中相 當常見 牌型</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>順子是由五張數字連續的牌所組成，在遊戲中屬於機率偏低的牌型。</t>
+          <t>三條是由三張同一個數字的牌所組成，出現的機率稍低。</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>順子 五張 數字 連續 牌 所 組成 遊戲 中屬 機率 偏低 牌型</t>
+          <t>三條 三張 同一 個 數字 牌 所 組成 出現 機率 稍低</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>同花是指五張牌都是同一個花色，雖然強度很高，但出現的機率依然偏低。</t>
+          <t>順子是由五張數字連續的牌所組成，在遊戲中屬於機率偏低的牌型。</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>同花 指五 張牌 同一 個 花色 雖然 強度 很 高 但 出現 機率 依然 偏低</t>
+          <t>順子 五張 數字 連續 牌 所 組成 遊戲 中屬 機率 偏低 牌型</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>葫蘆是由一個對子加上一個三條所組成，是一個非常強勢且出現機率較低的牌型。</t>
+          <t>同花是指五張牌都是同一個花色，雖然強度很高，但出現的機率依然偏低。</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>葫蘆 對子 加上 三條 所 組成 非常 強勢 且 出現 機率 較 低 牌型</t>
+          <t>同花 指五 張牌 同一 個 花色 雖然 強度 很 高 但 出現 機率 依然 偏低</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>四條是由四張同一個數字的牌所組成，屬於出現機率極低的強大牌型。</t>
+          <t>葫蘆是由一個對子加上一個三條所組成，是一個非常強勢且出現機率較低的牌型。</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>四條 四張 同一 個 數字 牌 所 組成 屬 出現 機率 極低 的強 大牌 型</t>
+          <t>葫蘆 對子 加上 三條 所 組成 非常 強勢 且 出現 機率 較 低 牌型</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>同花順的強度僅次於皇家同花順，是同花色加上順子的組合，出現的機率也是極度罕見。</t>
+          <t>四條是由四張同一個數字的牌所組成，屬於出現機率極低的強大牌型。</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>同花順 強度 僅次 皇家同花順 同 花色 加上 順子 組合 出現 機率 極度 罕見</t>
+          <t>四條 四張 同一 個 數字 牌 所 組成 屬 出現 機率 極低 的強 大牌 型</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>皇家同花順是德州撲克中最強的牌型，A_K_Q_J_10 的同花色組合而成，出現的機率極度罕見。</t>
+          <t>同花順的強度僅次於皇家同花順，是同花色加上順子的組合，出現的機率也是極度罕見。</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>皇家同花順 德州撲克 中 最強 牌型 a_k_q_j_10 同 花色 組合 而成 出現 機率 極度 罕見</t>
+          <t>同花順 強度 僅次 皇家同花順 同 花色 加上 順子 組合 出現 機率 極度 罕見</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>牌型大方向比大小A_K_Q_J_10_9_8_7_6_5_4_3_2，spade黑桃 、heart紅心、diamond方塊、club梅花</t>
+          <t>皇家同花順是德州撲克中最強的牌型，A_K_Q_J_10 的同花色組合而成，出現的機率極度罕見。</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>牌型 大方向 比 大小 a_k_q_j_10_9_8_7_6_5_4_3_2 spade 黑桃 heart 紅心 diamond 方塊 club 梅花</t>
+          <t>皇家同花順 德州撲克 中 最強 牌型 a_k_q_j_10 同 花色 組合 而成 出現 機率 極度 罕見</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>兩個玩家拿到同樣的牌型，首先比較主要牌型的大小（一對的話比對子的強度，兩對的話看較大的對子強度，三條的話看數位的強度）。･如果主要牌型相同，則比較其餘的牌。如果其餘的牌也相同的話，則平分底池。</t>
+          <t>牌型大方向比大小A_K_Q_J_10_9_8_7_6_5_4_3_2，spade黑桃 、heart紅心、diamond方塊、club梅花</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>兩個 玩家 拿到 同樣 牌型 首先 比較 主要 牌型 大小 一對 話 比 對子 強度 兩對 話 看 較 大 對子 強度 三條 話 看 數位 強度 如果 主要 牌型 相同 則比較 其餘 牌 如果 其餘 牌 相同 話 則 平分 底池</t>
+          <t>牌型 大方向 比 大小 a_k_q_j_10_9_8_7_6_5_4_3_2 spade 黑桃 heart 紅心 diamond 方塊 club 梅花</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>平局情況的底池分配：在平局的情況下，下注的籌碼被平分，並在排名第一的玩家之間平均分配。 但是，如果當時的籌碼總數有除不盡的情況，則一般常見的規則是把除盡後剩下的籌碼分給最先叫注的人（也就是「位置不佳的人」）。</t>
+          <t>兩個玩家拿到同樣的牌型，首先比較主要牌型的大小（一對的話比對子的強度，兩對的話看較大的對子強度，三條的話看數位的強度）。･如果主要牌型相同，則比較其餘的牌。如果其餘的牌也相同的話，則平分底池。</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>平局 情況 底池 分配 平局 情況 下 下注 籌碼 平分 並在 排名 第一 玩家 之間 平均分配 但是 如果 當時 籌碼 總數 有 除 不 盡 情況 則 一般 常見 規則 把 除 盡 後 剩下 籌碼 分給 最先 叫注 人 就是 位置 不佳 人</t>
+          <t>兩個 玩家 拿到 同樣 牌型 首先 比較 主要 牌型 大小 一對 話 比 對子 強度 兩對 話 看 較 大 對子 強度 三條 話 看 數位 強度 如果 主要 牌型 相同 則比較 其餘 牌 如果 其餘 牌 相同 話 則 平分 底池</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>位置的基本觀念：首先叫注的位置是不利的，而後面的位置被認為是有利的。 越是後面的玩家越有利，因為可以在查看其他玩家的動作之後自己做判斷。在不完整的訊息游戲（看不見對手的手牌）中，訊息量越多越有利，因此說可以在獲取其他玩家的訊息後採取行動的靠後位置是一個優勢。</t>
+          <t>平局情況的底池分配：在平局的情況下，下注的籌碼被平分，並在排名第一的玩家之間平均分配。 但是，如果當時的籌碼總數有除不盡的情況，則一般常見的規則是把除盡後剩下的籌碼分給最先叫注的人（也就是「位置不佳的人」）。</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>位置 基本 觀念 首先 叫注 位置 不利 而後面 位置 認為 有利 越是 後 面 玩家 越 有利 因為 可以 查看 其他 玩家 動作 之 後 自己 做判斷 不 完整 訊息 游戲 看不見 對手 手牌 中 訊息量 越多越 有利 因此 說 可以 獲取 其他 玩家 訊息 後 採取 行動 靠 後 位置 優勢</t>
+          <t>平局 情況 底池 分配 平局 情況 下 下注 籌碼 平分 並在 排名 第一 玩家 之間 平均分配 但是 如果 當時 籌碼 總數 有 除 不 盡 情況 則 一般 常見 規則 除 盡 後 剩下 籌碼 分給 最先 叫注 人 就是 位置 不佳 人</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SB（小盲位）：位於 BTN 莊家左側的位置。 在這個位置必須下半盲注。 翻牌前可以在 BTN 莊家位行動後進行棄牌，跟注和加注等操作。 翻牌後，必須最先下決定的位置，所以可以說是一個不利的位置。 另外，即使在翻牌前，也要注意在後面的 BB 大盲位置的行動，因此很難採取激進的叫注動作。</t>
+          <t>位置的基本觀念：首先叫注的位置是不利的，而後面的位置被認為是有利的。 越是後面的玩家越有利，因為可以在查看其他玩家的動作之後自己做判斷。在不完整的訊息游戲（看不見對手的手牌）中，訊息量越多越有利，因此說可以在獲取其他玩家的訊息後採取行動的靠後位置是一個優勢。</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>sb 小盲位 位 btn 莊家 左側 位置 這個 位置 必須 下 半 盲注 翻牌前 可以 btn 莊家 位 行動 後 進行 棄牌 跟注 和 加注 等 操作 翻牌後 必須 最先 下 決定 位置 所以 可以 說 不利 位置 另外 即使 翻牌前 要 注意 在後面 bb 大盲位 置 行動 因此 很難 採取 激進 叫注 動作</t>
+          <t>位置 基本 觀念 首先 叫注 位置 不利 而後面 位置 認為 有利 越是 後 面 玩家 越 有利 因為 可以 查看 其他 玩家 動作 之 後 自己 做判斷 不 完整 訊息 游戲 看不見 對手 手牌 中 訊息量 越多越 有利 因此 說 可以 獲取 其他 玩家 訊息 後 採取 行動 靠 後 位置 優勢</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BB（大盲位）：位於 SB 小盲左側的位置。 在這個位置必須下盲注。 翻牌前可以在 SB 小盲位行動後進行棄牌，跟注和加注等操作。 翻牌後，您需要在 SB 小盲位旁邊採取行動。 在翻牌前，您可以在最後階段採取行動，但是如果在翻牌後，除了 SB 小盲位以外，該位置都被認為是不利的，因此它並不是一個好位置。</t>
+          <t>SB（小盲位）：位於 BTN 莊家左側的位置。 在這個位置必須下半盲注。 翻牌前可以在 BTN 莊家位行動後進行棄牌，跟注和加注等操作。 翻牌後，必須最先下決定的位置，所以可以說是一個不利的位置。 另外，即使在翻牌前，也要注意在後面的 BB 大盲位置的行動，因此很難採取激進的叫注動作。</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>bb 大盲位 位 sb 小盲 左側 位置 這個 位置 必須 下 盲注 翻牌前 可以 sb 小盲位 行動 後 進行 棄牌 跟注 和 加注 等 操作 翻牌後 您 需要 sb 小盲位 旁邊 採取 行動 翻牌前 您 可以 最後階段 採取 行動 但是 如果 翻牌後 除了 sb 小盲位 以外 該 位置 認為 不利 因此 它並 不是 好 位置</t>
+          <t>sb 小盲位 位 btn 莊家 左側 位置 這個 位置 必須 下 半 盲注 翻牌前 可以 btn 莊家 位 行動 後 進行 棄牌 跟注 和 加注 等 操作 翻牌後 必須 最先 下 決定 位置 所以 可以 說 不利 位置 另外 即使 翻牌前 要 注意 在後面 bb 大盲位 置 行動 因此 很難 採取 激進 叫注 動作</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UTG（槍口位）：位於 BB 大盲左側的位置。 必須在翻牌前最先採取行動，並且由於翻牌後除了 SB 和 BB 之外，該位置都是不利的，因此從槍口指向的角度來看，這是危險的位置。 由於沒有任何先叫注對手的訊息，因此在游戲中唯一可以利用的訊息就是自己的手牌（底牌）。 因此，該位置如果要採取下注行為的話需要很強的手牌。</t>
+          <t>BB（大盲位）：位於 SB 小盲左側的位置。 在這個位置必須下盲注。 翻牌前可以在 SB 小盲位行動後進行棄牌，跟注和加注等操作。 翻牌後，您需要在 SB 小盲位旁邊採取行動。 在翻牌前，您可以在最後階段採取行動，但是如果在翻牌後，除了 SB 小盲位以外，該位置都被認為是不利的，因此它並不是一個好位置。</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>utg 槍口位 位 bb 大盲 左側 位置 必須 翻牌前 最先 採取 行動 並且 翻牌後 除了 sb 和 bb 之外 該 位置 不利 因此 從 槍口 指向 角度 來 看 這是 危險 位置 沒 有 任何 先 叫注 對手 訊息 因此 游戲 中 唯一 可以 利用 訊息 就是 自己 手牌 底牌 因此 該 位置 如果 要 採取 下注 行為 話 需要 很強 手牌</t>
+          <t>bb 大盲位 位 sb 小盲 左側 位置 這個 位置 必須 下 盲注 翻牌前 可以 sb 小盲位 行動 後 進行 棄牌 跟注 和 加注 等 操作 翻牌後 您 需要 sb 小盲位 旁邊 採取 行動 翻牌前 您 可以 最後階段 採取 行動 但是 如果 翻牌後 除了 sb 小盲位 以外 該 位置 認為 不利 因此 它並 不是 好 位置</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EP（早期位）：指需要及早採取行動的位置。 它取決於坐在桌子上的人數。 在10人桌的情況下，UTG 和其左邊的兩個人通常稱為早期位。 對于6人桌，只有UTG 處于早期位。</t>
+          <t>UTG（槍口位）：位於 BB 大盲左側的位置。 必須在翻牌前最先採取行動，並且由於翻牌後除了 SB 和 BB 之外，該位置都是不利的，因此從槍口指向的角度來看，這是危險的位置。 由於沒有任何先叫注對手的訊息，因此在游戲中唯一可以利用的訊息就是自己的手牌（底牌）。 因此，該位置如果要採取下注行為的話需要很強的手牌。</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ep 早期位 需要 及早 採取 行動 位置 它 取決 坐在 桌子 上 人數 10 人桌 情況 下 utg 和 其 左邊 兩個 人 通常 稱為 早期位 對于 6 人桌 只有 utg 處于 早期位</t>
+          <t>utg 槍口位 位 bb 大盲 左側 位置 必須 翻牌前 最先 採取 行動 並且 翻牌後 除了 sb 和 bb 之外 該 位置 不利 因此 從 槍口 指向 角度 來 看 這是 危險 位置 沒 有 任何 先 叫注 對手 訊息 因此 游戲 中 唯一 可以 利用 訊息 就是 自己 手牌 底牌 因此 該 位置 如果 要 採取 下注 行為 話 需要 很強 手牌</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MP（中期位）：指每個回合在中間採取行動的位置。 在10人桌的情況下，通常將在翻牌前從第4到第6的這3人位置叫做中期位。 對于6人桌，UTG 的左側2個人屬於中間位。</t>
+          <t>EP（早期位）：指需要及早採取行動的位置。 它取決於坐在桌子上的人數。 在10人桌的情況下，UTG 和其左邊的兩個人通常稱為早期位。 對于6人桌，只有UTG 處于早期位。</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>mp 中期位 每個 回合 中間 採取 行動 位置 10 人桌 情況 下 通常 將在 翻牌前 從 第 4 到 第 6 這 3 人 位置 叫做 中期位 對于 6 人桌 utg 左側 2 個 人屬 中間 位</t>
+          <t>ep 早期位 需要 及早 採取 行動 位置 它 取決 坐在 桌子 上 人數 10 人桌 情況 下 utg 和 其 左邊 兩個 人 通常 稱為 早期位 對于 6 人桌 只有 utg 處于 早期位</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CO（關煞位）：指的是 BTN 莊家位的前一個位置。</t>
+          <t>MP（中期位）：指每個回合在中間採取行動的位置。 在10人桌的情況下，通常將在翻牌前從第4到第6的這3人位置叫做中期位。 對于6人桌，UTG 的左側2個人屬於中間位。</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>co 關煞位 btn 莊家 位 前 位置</t>
+          <t>mp 中期位 每個 回合 中間 採取 行動 位置 10 人桌 情況 下 通常 將在 翻牌前 從 第 4 到 第 6 3 人 位置 叫做 中期位 對于 6 人桌 utg 左側 2 個 人屬 中間 位</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BTN（莊家按鈕位）：指的是每回合可以最後採取行動的位置，被認為是最佳位置。 在許多情況下，這個位置的玩家前面都會放置一枚寫著 DEALER 字樣的圓形按鈕。 不管是線上還是線下，這個位置都會做標記。</t>
+          <t>CO（關煞位）：指的是 BTN 莊家位的前一個位置。</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>btn 莊家 按鈕位 每 回合 可以 最後採取 行動 位置 認為 最佳 位置 在許 多情 況下 這個 位置 玩家 前面 會 放置 一枚 寫著 dealer 字樣 圓形 按鈕 不管 線 上 還是 線 下 這個 位置 會 做 標記</t>
+          <t>co 關煞位 btn 莊家 位 前 位置</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>all_in（全下）：全下意味著把自己手上的籌碼全部下注在某牌桌上。 一旦全下，就不能下注或跟注，也不能棄牌，自動過渡到亮牌階段。 其餘玩家將繼續照常進行。</t>
+          <t>BTN（莊家按鈕位）：指的是每回合可以最後採取行動的位置，被認為是最佳位置。 在許多情況下，這個位置的玩家前面都會放置一枚寫著 DEALER 字樣的圓形按鈕。 不管是線上還是線下，這個位置都會做標記。</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>all_in 全 下 全 下 意味著 把 自己 手上 籌碼 全部 下注 某牌 桌上 一旦 全 下 不能 下注 或 跟注 不能 棄牌 自動 過渡 到 亮牌 階段 其餘 玩家 將繼續 照常 進行</t>
+          <t>btn 莊家 按鈕位 每 回合 可以 最後採取 行動 位置 認為 最佳 位置 在許 多情 況下 這個 位置 玩家 前面 放置 一枚 寫著 dealer 字樣 圓形 按鈕 不管 線 上 還是 線 下 這個 位置 做 標記</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bet（下注）：下注意味著加大籌碼。 如果在前面的玩家尚未進行下注，則下注是該玩家可以採取的行動之一。 一個玩家只有在沒有其他人先進行下注的情況下才能下注。 如果已經有玩家下注，則玩家必須進行跟注動作或者有需要的話可以加注。</t>
+          <t>all_in（全下）：全下意味著把自己手上的籌碼全部下注在某牌桌上。 一旦全下，就不能下注或跟注，也不能棄牌，自動過渡到亮牌階段。 其餘玩家將繼續照常進行。</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>bet 下注 下注 意味著 加大 籌碼 如果 前面 玩家 尚未 進行 下注 則 下注 該 玩家 可以 採取 行動 之一 玩家 只有 沒 有 其他人 先 進行 下注 情況 下 才能 下注 如果 已經 有 玩家 下注 則 玩家 必須 進行 跟注 動作 或者 有 需要 話 可以 加注</t>
+          <t>all_in 全 下 全 下 自己 手上 籌碼 全部 下注 某牌 桌上 一旦 全 下 不能 下注 或 跟注 不能 棄牌 自動 過渡 到 亮牌 階段 其餘 玩家 將繼續 照常 進行</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Buy_in（買入）：參與游戲所需的金額。 對于諸如賭場的現金游戲，最低買入費由表格設定。 對于賽事，分為獎池和支付給主辦方的參與費。</t>
+          <t>Bet（下注）：下注意味著加大籌碼。 如果在前面的玩家尚未進行下注，則下注是該玩家可以採取的行動之一。 一個玩家只有在沒有其他人先進行下注的情況下才能下注。 如果已經有玩家下注，則玩家必須進行跟注動作或者有需要的話可以加注。</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>buy _ in 買入 參與 游戲 所 需 金額 對于 諸如 賭場 現金游戲 最低 買入費 表格 設定 對于 賽事 分為 獎池 和 支付 給主 辦方 參與費</t>
+          <t>bet 下注 下注 加大 籌碼 如果 前面 玩家 尚未 進行 下注 則 下注 該 玩家 可以 採取 行動 之一 玩家 只有 沒 有 其他人 先 進行 下注 情況 下 才能 下注 如果 已經 有 玩家 下注 則 玩家 必須 進行 跟注 動作 或者 有 需要 話 可以 加注</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bank_roll（總資金）：玩家的資金就是他用來玩撲克的全部金錢。 即准備的資金總額。 在線撲克中，指的是玩家帳戶裡所擁有的資金。</t>
+          <t>Buy_in（買入）：參與游戲所需的金額。 對于諸如賭場的現金游戲，最低買入費由表格設定。 對于賽事，分為獎池和支付給主辦方的參與費。</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>bank_roll 總資金 玩家 資金 就是 他用 來 玩 撲克 全部 金錢 即 准備 資金 總額 線 撲克中 玩家 帳戶裡 所 擁有 資金</t>
+          <t>buy _ in 買入 參與 游戲 所 需 金額 對于 諸如 賭場 現金游戲 最低 買入費 表格 設定 對于 賽事 分為 獎池 和 支付 給主 辦方 參與費</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Blind（盲注）：盲注是撲克游戲中強制下注的一種形式。 是必須在發牌前支付的賭注。 每回合由兩名玩家支付，但不是固定玩家支付，每一回合輪流變化。 通常，兩個賭注具有相同的大小，或者一個賭注大於另一個賭注。 後者稱為「大盲注和小盲注」。</t>
+          <t>Bank_roll（總資金）：玩家的資金就是他用來玩撲克的全部金錢。 即准備的資金總額。 在線撲克中，指的是玩家帳戶裡所擁有的資金。</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>blind 盲注 盲注 撲克游 戲中 強制 下注 一種 形式 必須 發牌 前 支付 賭注 每 回合 兩名 玩家 支付 但 不是 固定 玩家 支付 每一 回合 輪流 變化 通常 兩個 賭注 具有 相同 大小 或者 賭注 大於 另 賭注 後 者 稱 大盲注 和 小盲注</t>
+          <t>bank_roll 總資金 玩家 資金 就是 他用 來 玩 撲克 全部 金錢 即 准備 資金 總額 線 撲克中 玩家 帳戶裡 所 擁有 資金</t>
         </is>
       </c>
     </row>
@@ -1759,57 +1759,57 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Board（公共牌）：在使用公共牌的游戲中，Board一般指的是所有公共牌。 例如，在德州撲克中，由翻牌，轉牌和河牌組成。</t>
+          <t>Blind（盲注）：盲注是撲克游戲中強制下注的一種形式。 是必須在發牌前支付的賭注。 每回合由兩名玩家支付，但不是固定玩家支付，每一回合輪流變化。 通常，兩個賭注具有相同的大小，或者一個賭注大於另一個賭注。 後者稱為「大盲注和小盲注」。</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>board 公共牌 使用 公共牌 游戲 中 board 一般 所有 公共牌 例如 德州撲克 中 翻牌 轉牌 和 河牌 組成</t>
+          <t>blind 盲注 盲注 撲克游 戲中 強制 下注 一種 形式 必須 發牌 前 支付 賭注 每 回合 兩名 玩家 支付 但 不是 固定 玩家 支付 每一 回合 輪流 變化 通常 兩個 賭注 具有 相同 大小 或者 賭注 大於 另 賭注 後 者 稱 大盲注 和 小盲注</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Button（按鈕）：按鈕，或者莊家按鈕，是一個提示，顯示當前誰是莊家。 莊家坐在的位置也稱為按鈕位。 或者說「莊家即按鈕」。</t>
+          <t>Board（公共牌）：在使用公共牌的游戲中，Board一般指的是所有公共牌。 例如，在德州撲克中，由翻牌，轉牌和河牌組成。</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>button 按鈕 按鈕 或者 莊家 按鈕 提示 顯示 當前 誰 莊家 莊家 坐在 位置 稱 按鈕位 或者 說 莊家 即 按鈕</t>
+          <t>board 公共牌 使用 公共牌 游戲 中 board 一般 所有 公共牌 例如 德州撲克 中 翻牌 轉牌 和 河牌 組成</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bad_beat（小概率失敗）：Bad_beat 是指拿到好牌非常有優勢的玩家在不太可能的情況下輸掉。 正常失敗和小概率失敗之間的界限因玩家而異。 </t>
+          <t>Button（按鈕）：按鈕，或者莊家按鈕，是一個提示，顯示當前誰是莊家。 莊家坐在的位置也稱為按鈕位。 或者說「莊家即按鈕」。</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>bad _ beat 小 概率 失敗 bad _ beat 拿到 好牌 非常 有 優勢 玩家 不太可能 情況 下輸 掉 正常 失敗 和 小 概率 失敗 之間 界限 因 玩家 而異</t>
+          <t>button 按鈕 按鈕 或者 莊家 按鈕 提示 顯示 當前 誰 莊家 莊家 坐在 位置 稱 按鈕位 或者 說 莊家 即 按鈕</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Blank（空白）：空白或磚塊指的是不會形成任何牌型的公共牌。 「轉牌是空白」表示轉牌沒有改變游戲狀況。 例如，在3高牌（花色不同的牌）翻牌後，轉牌出現2，表示為空白。</t>
+          <t xml:space="preserve">Bad_beat（小機率失敗）：Bad_beat 是指拿到好牌非常有優勢的玩家在不太可能的情況下輸掉。 正常失敗和小機率失敗之間的界限因玩家而異。 </t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>blank 空白 空白 或 磚塊 不會 形成 任何 牌型 公共牌 轉牌 空白 表示 轉牌 沒有 改變 游戲 狀況 例如 3 高牌 花色 不同 牌 翻牌後 轉牌 出現 2 表示 空白</t>
+          <t>bad _ beat 小 機率 失敗 bad _ beat 拿到 好牌 非常 有 優勢 玩家 不太可能 情況 下輸 掉 正常 失敗 和 小 機率 失敗 之間 界限 因 玩家 而異</t>
         </is>
       </c>
     </row>
@@ -1819,27 +1819,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bust_out（出局）：淘汰或出局意味著失去自己的全部籌碼或輸掉賽事。 淘汰某人意味著把某人從桌子排除或從賽事中擊敗。</t>
+          <t>Blank（空白）：空白或磚塊指的是不會形成任何牌型的公共牌。 「轉牌是空白」表示轉牌沒有改變游戲狀況。 例如，在3高牌（花色不同的牌）翻牌後，轉牌出現2，表示為空白。</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>bust _ out 出局 淘汰 或 出局 意味著 失去 自己 全部 籌碼 或 輸掉 賽事 淘汰 某人 意味著 把 某人 從 桌子 排除 或 從 賽事 中擊敗</t>
+          <t>blank 空白 空白 或 磚塊 不會 形成 任何 牌型 公共牌 轉牌 空白 表示 轉牌 沒有 改變 游戲 狀況 例如 3 高牌 花色 不同 牌 翻牌後 轉牌 出現 2 表示 空白</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Call（跟注）：跟上一位玩家投入相同籌碼。 跟注是相對于對手的加注可以采取的行動之一。</t>
+          <t>Bust_out（出局）：淘汰或出局意味著失去自己的全部籌碼或輸掉賽事。 淘汰某人意味著把某人從桌子排除或從賽事中擊敗。</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>call 跟注 跟上 一位 玩家 投入 相同 籌碼 跟注 相 于 對手 加注 可以 采取 行動 之一</t>
+          <t>bust _ out 出局 淘汰 或 出局 失去 自己 全部 籌碼 或 輸掉 賽事 淘汰 某人 某人 從 桌子 排除 或 從 賽事 中擊敗</t>
         </is>
       </c>
     </row>
@@ -1849,102 +1849,102 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Check（看牌）：前面無人下注，自己也不下注，也叫「看牌」或「過牌」。 看牌是玩家可以採取的行動之一。 不進行加注動作的玩家可以選擇看牌動作。</t>
+          <t>Call（跟注）：跟上一位玩家投入相同籌碼。 跟注是相對于對手的加注可以采取的行動之一。</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>check 看牌 前面 無人 下注 自己 不 下注 叫 看牌 或 過牌 看牌 玩家 可以 採取 行動 之一 不 進行 加注 動作 玩家 可以 選擇 看牌 動作</t>
+          <t>call 跟注 跟上 一位 玩家 投入 相同 籌碼 跟注 相 于 對手 加注 可以 采取 行動 之一</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cut_off（關煞位）：在有規定莊家按鈕位的游戲中，關煞位在按鈕位的右邊。</t>
+          <t>Check（看牌）：前面無人下注，自己也不下注，也叫「看牌」或「過牌」。 看牌是玩家可以採取的行動之一。 不進行加注動作的玩家可以選擇看牌動作。</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>cut_off 關煞位 有 規定 莊家 按鈕位 游戲 中 關煞位 按鈕位 右邊</t>
+          <t>check 看牌 前面 無人 下注 自己 不 下注 叫 看牌 或 過牌 看牌 玩家 可以 採取 行動 之一 不 進行 加注 動作 玩家 可以 選擇 看牌 動作</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cap（上限）：上限是您在一局中可以加的最後一次加注，或者是一局中可以下注的最大金額。 通常在一局中限制第三，第四或第五次加注。 最後加注的成為上限。</t>
+          <t>Cut_off（關煞位）：在有規定莊家按鈕位的游戲中，關煞位在按鈕位的右邊。</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>cap 上限 上限 您 一局 中 可以 加 最 後 一次 加注 或者 一局 中 可以 下注 最大 金額 通常 一局 中 限制 第三 第四 或 第五次 加注 最 後 加注 成為 上限</t>
+          <t>cut_off 關煞位 有 規定 莊家 按鈕位 游戲 中 關煞位 按鈕位 右邊</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Community_cards（公共牌）：由荷官發出的桌上的玩家共有的牌。</t>
+          <t>Cap（上限）：上限是您在一局中可以加的最後一次加注，或者是一局中可以下注的最大金額。 通常在一局中限制第三，第四或第五次加注。 最後加注的成為上限。</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>community_cards 公共牌 荷官 發出 桌上 玩家 共有 牌</t>
+          <t>cap 上限 上限 您 一局 中 可以 加 最 後 一次 加注 或者 一局 中 可以 下注 最大 金額 通常 一局 中 限制 第三 第四 或 第五次 加注 最 後 加注 成為 上限</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Check_Raise（看牌加注）：看牌加注是一種打法，指的是「玩家先看牌然後在下一個對手下注時加注」。</t>
+          <t>Community_cards（公共牌）：由荷官發出的桌上的玩家共有的牌。</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>check_raise 看牌 加注 看牌 加注 一種 打法 玩家 先看 牌然 後 下 對手 下注 時 加注</t>
+          <t>community_cards 公共牌 荷官 發出 桌上 玩家 共有 牌</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Draw（聽牌）：聽牌是指未完成的組合，還需要1張或1張以上的牌才能組成特定的牌型。</t>
+          <t>Check_Raise（看牌加注）：看牌加注是一種打法，指的是「玩家先看牌然後在下一個對手下注時加注」。</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>draw 聽牌 聽牌 指未 完成 組合 還 需要 1 張 或 1 張 以上 牌 才能 組 成特定 牌型</t>
+          <t>check_raise 看牌 加注 看牌 加注 一種 打法 玩家 先看 牌然 後 下 對手 下注 時 加注</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Dealer（荷官）：荷官指的是發牌的人。</t>
+          <t>Draw（聽牌）：聽牌是指未完成的組合，還需要1張或1張以上的牌才能組成特定的牌型。</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>dealer 荷官 荷官 發牌 人</t>
+          <t>draw 聽牌 聽牌 指未 完成 組合 還 需要 1 張 或 1 張 以上 牌 才能 組 成特定 牌型</t>
         </is>
       </c>
     </row>
@@ -1954,327 +1954,327 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Drawing_dead（聽死牌）：玩家就算發牌之後也沒有勝算的話，就稱作「他在聽死牌」。</t>
+          <t>Dealer（荷官）：荷官指的是發牌的人。</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>drawing_dead 聽死牌 玩家 就算 發牌 之 後 沒 有 勝算 話 稱作 他 聽 死牌</t>
+          <t>dealer 荷官 荷官 發牌 人</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Edge（優勢）：「擁有優勢」意味著比其他玩家更具優勢。 例如，好的手牌比弱的手牌有優勢。 技術水準高或桌上位置好的玩家也有優勢。</t>
+          <t>Drawing_dead（聽死牌）：玩家就算發牌之後也沒有勝算的話，就稱作「他在聽死牌」。</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>edge 優勢 擁有 優勢 意味著 比 其他 玩家 更具 優勢 例如 好 手牌 比弱 手牌 有 優勢 技術 水準 高 或 桌上 位置 好 玩家 有 優勢</t>
+          <t>drawing_dead 聽死牌 玩家 就算 發牌 之 後 沒 有 勝算 話 稱作 他 聽 死牌</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Early（早期）：在玩家相對于荷官的相對位置決定游戲順序的游戲中，早期位是必須首先採取行動的玩家。 也稱為UTG（槍口位）</t>
+          <t>Edge（優勢）：「擁有優勢」意味著比其他玩家更具優勢。  技術水準高或桌上位置好的玩家也有優勢。</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>early 早期 玩家 相對于 荷官 相 位置 決定 游戲 順序 游戲 中 早期位 必須 首先 採取 行動 玩家 稱 utg 槍口位</t>
+          <t>edge 優勢 擁有 優勢 比 其他 玩家 更具 優勢 技術 水準 高 或 桌上 位置 好 玩家 有 優勢</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Flop（翻牌）：在德州撲克和奧馬哈等使用公共牌的撲克游戲中，翻牌指的是前三張公共牌。</t>
+          <t>Early（早期）：在玩家相對于荷官的相對位置決定游戲順序的游戲中，早期位是必須首先採取行動的玩家。 也稱為UTG（槍口位）</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>flop 翻牌 德州撲克 和 奧馬哈 等 使用 公共牌 撲克游戲 中 翻牌 前三張 公共牌</t>
+          <t>early 早期 玩家 相對于 荷官 相 位置 決定 游戲 順序 游戲 中 早期位 必須 首先 採取 行動 玩家 稱 utg 槍口位</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Fold（棄牌）：棄牌的玩家放置其牌，並在本回合中退出該賽事。 該玩家已經下注的籌碼留在底池中，可以從下一輪重新加入游戲。</t>
+          <t>Flop（翻牌）：在德州撲克和奧馬哈等使用公共牌的撲克游戲中，翻牌指的是前三張公共牌。</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>fold 棄牌 棄牌 玩家 放置 其牌 並在 本 回合 中 退出 該賽 事 該 玩家 已經 下注 籌碼 留在 底池 中 可以 從下 一輪 重新加入 游戲</t>
+          <t>flop 翻牌 德州撲克 和 奧馬哈 等 使用 公共牌 撲克游戲 中 翻牌 前三張 公共牌</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fish（菜鳥）：Fish 指的是菜鳥。  Fish 指沒有策略，甚至還會採取負期望的行動的玩家。  菜鳥用很爛的牌入池，還頻繁下注。 </t>
+          <t>Fold（棄牌）：棄牌的玩家放置其牌，並在本回合中退出該賽事。 該玩家已經下注的籌碼留在底池中，可以從下一輪重新加入游戲。</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>fish 菜 鳥 fish 菜 鳥 fish 指沒有 策略 甚至 還會 採取負 期望 行動 玩家 菜 鳥用 很爛 牌入 池 還頻 繁 下注</t>
+          <t>fold 棄牌 棄牌 玩家 放置 其牌 並在 本 回合 中 退出 該賽 事 該 玩家 已經 下注 籌碼 留在 底池 中 可以 從下 一輪 重新加入 游戲</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Freeroll（免費賽）：Freeroll 免費賽是指具有贊助獎品或有贊助商的不需要買入的賽事。 Freeroll 免費賽指2名玩家擁有同等實力的手牌聽牌，其中1名玩家組成牌型的話將拿走全部獎池的情況。 （第二個玩家聽牌沒有擊中）。</t>
+          <t xml:space="preserve">Fish（菜鳥）：Fish 指的是菜鳥。  Fish 指沒有策略，甚至還會採取負期望的行動的玩家。  菜鳥用很爛的牌入池，還頻繁下注。 </t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>freeroll 免費賽 freeroll 免費賽 具有 贊助 獎品 或 有 贊助商 不 需要 買入 賽事 freeroll 免費賽 2 名 玩家 擁有 同等 實力 手牌 聽牌 其中 1 名 玩家 組成 牌型 話將 拿走 全部 獎池 情況 第二 個 玩家 聽牌 沒有擊 中</t>
+          <t>fish 菜 鳥 fish 菜 鳥 fish 指沒有 策略 甚至 還會 採取負 期望 行動 玩家 菜 鳥用 很爛 牌入 池 還頻 繁 下注</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Grind（安全打法）：安全打法指的是不願冒太大風險，根據一定的下注限額持續取得利益的一種打法。 「Grinder」和「Rounder」這兩個術語是指，為了賺取自己的收入一部分或者全額（即使可以採取高風險高回報的打法的 時候）進行的安全打法。</t>
+          <t>Freeroll（免費賽）：Freeroll 免費賽是指具有贊助獎品或有贊助商的不需要買入的賽事。 Freeroll 免費賽指2名玩家擁有同等實力的手牌聽牌，其中1名玩家組成牌型的話將拿走全部獎池的情況。 （第二個玩家聽牌沒有擊中）。</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>grind 安全 打法 安全 打法 不願 冒 太大風險 一定 下注 限額 持續 取得 利益 一種 打法 grinder 和 rounder 這兩個術語 賺取 自己 收入 一部分 或者 全額 即使 可以 採取 高風險 高 回報 打法 時候 進行 安全 打法</t>
+          <t>freeroll 免費賽 freeroll 免費賽 具有 贊助 獎品 或 有 贊助商 不 需要 買入 賽事 freeroll 免費賽 2 名 玩家 擁有 同等 實力 手牌 聽牌 其中 1 名 玩家 組成 牌型 話將 拿走 全部 獎池 情況 第二 個 玩家 聽牌 沒有擊 中</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>heads_up（單挑）：只有2個玩家玩的撲克游戲稱為「單挑」。 單挑游戲是不規則的撲克形式，將是最激烈的戰鬥。 因為玩家無力等待強牌，所以除了相信自己的打法運氣和發現對手的弱點外，他們別無選擇。</t>
+          <t>Grind（安全打法）：安全打法指的是不願冒太大風險，根據一定的下注限額持續取得利益的一種打法。 「Grinder」和「Rounder」這兩個術語是指，為了賺取自己的收入一部分或者全額（即使可以採取高風險高回報的打法的 時候）進行的安全打法。</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>heads_up 單挑 只有 2 個 玩家 玩 撲克游 戲稱 單挑 單挑游戲 不 規則 撲克 形式 將是 最 激烈 戰鬥 因為 玩家 無力 等待 強牌 所以 除了 相信 自己 打法 運氣 和 發現 對手 弱點 外 他們 別無選擇</t>
+          <t>grind 安全 打法 安全 打法 不願 冒 太大風險 一定 下注 限額 持續 取得 利益 一種 打法 grinder 和 rounder 這兩個術語 賺取 自己 收入 一部分 或者 全額 即使 可以 採取 高風險 高 回報 打法 時候 進行 安全 打法</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>hole_cards（手牌）：手牌指的是只有自己可以看見的卡牌。 比如，德州撲克中指的是荷官發給自己的2張牌。</t>
+          <t>heads_up（單挑）：只有2個玩家玩的撲克游戲稱為「單挑」。 單挑游戲是不規則的撲克形式，將是最激烈的戰鬥。 因為玩家無力等待強牌，所以除了相信自己的打法運氣和發現對手的弱點外，他們別無選擇。</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>hole_cards 手牌 手牌 只有 自己 可以 看見 卡牌 比如 德州撲克 中指 荷官 發給 自己 2 張牌</t>
+          <t>heads_up 單挑 只有 2 個 玩家 玩 撲克游 戲稱 單挑 單挑游戲 不 規則 撲克 形式 將是 最 激烈 戰鬥 因為 玩家 無力 等待 強牌 所以 除了 相信 自己 打法 運氣 和 發現 對手 弱點 外 他們 別無選擇</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Kicker（踢牌）：踢牌者是指組成撲克牌型的5張牌以外的1張牌，但是如果有2手牌具有相等值的牌型組合，則 其作用是確定這2手牌的強弱高下。 因此，少於5張牌型組合的牌才能使用踢牌。 也就是說，僅適用于四條，三條，一對（兩對）和高牌。 如果兩個玩家的手牌相等，則踢牌確定哪個玩家是獲勝者。 最高的踢牌是最強的踢牌。 狹義是有且只有一張踢牌。 也就是說，當兩個玩家的手牌相似時，只有那張踢牌才能決定哪個更強。 如果玩家擁有完全相同的一手牌，則最高的非組合牌將成為踢牌，他們將平分底池。</t>
+          <t>hole_cards（手牌）：手牌指的是只有自己可以看見的卡牌。 比如，德州撲克中指的是荷官發給自己的2張牌。</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>kicker 踢牌 踢牌 者 組成 撲克 牌型 5 張牌 以外 1 張牌 但是 如果 有 2 手牌 具有 相等值 牌型 組合 則 其 作用 確定 這 2 手牌 強弱 高下 因此 少 5 張 牌型 組合 牌 才能 使用 踢牌 就是 說 僅適 用于 四條 三條 一對 兩對 和 高牌 如果 兩個 玩家 手牌 相等 則 踢牌 確定 哪個 玩家 獲勝者 最高 踢牌 最強 踢牌 狹義是 有且 只有 一張 踢牌 就是 說 當兩個 玩家 手牌 相似 時 只有 那張 踢牌 才能 決定 哪個 更強 如果 玩家 擁有 完全相同 一手 牌 則 最高 非 組合牌 將成 踢牌 他們將 平分 底池</t>
+          <t>hole_cards 手牌 手牌 只有 自己 可以 看見 卡牌 比如 德州撲克 中指 荷官 發給 自己 2 張牌</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Limit（限額）：限額是下注金額或下注額的另一個術語。 </t>
+          <t>Kicker（踢牌）：踢牌者是指組成撲克牌型的5張牌以外的1張牌，但是如果有2手牌具有相等值的牌型組合，則 其作用是確定這2手牌的強弱高下。 因此，少於5張牌型組合的牌才能使用踢牌。 也就是說，僅適用于四條，三條，一對（兩對）和高牌。 如果兩個玩家的手牌相等，則踢牌確定哪個玩家是獲勝者。 最高的踢牌是最強的踢牌。 狹義是有且只有一張踢牌。 也就是說，當兩個玩家的手牌相似時，只有那張踢牌才能決定哪個更強。 如果玩家擁有完全相同的一手牌，則最高的非組合牌將成為踢牌，他們將平分底池。</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>limit 限額 限額 下注 金額 或 下注 額 另 一個術語</t>
+          <t>kicker 踢牌 踢牌 者 組成 撲克 牌型 5 張牌 以外 1 張牌 但是 如果 有 2 手牌 具有 相等值 牌型 組合 則 其 作用 確定 2 手牌 強弱 高下 因此 少 5 張 牌型 組合 牌 才能 使用 踢牌 就是 說 僅適 用于 四條 三條 一對 兩對 和 高牌 如果 兩個 玩家 手牌 相等 則 踢牌 確定 哪個 玩家 獲勝者 最高 踢牌 最強 踢牌 狹義是 有且 只有 一張 踢牌 就是 說 當兩個 玩家 手牌 相似 時 只有 那張 踢牌 才能 決定 哪個 更強 如果 玩家 擁有 完全相同 一手 牌 則 最高 非 組合牌 將成 踢牌 他們將 平分 底池</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Late（後期位）：在游戲中玩家行為順序由莊家的位置決定的情況下，後期位置是指最後兩個位置（關煞位和按鈕位）。 處在這些位置的玩家比其他位置的玩家要有優勢。 因為他們可以在看了其他前面玩家的行動之後自己再採取相應的行動。</t>
+          <t xml:space="preserve">Limit（限額）：限額是下注金額或下注額的另一個術語。 </t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>late 後期位 游戲 中 玩家 行為 順序 莊家 位置 決定 情況 下 後期位 置 最後兩個 位置 關煞位 和 按鈕位 處 這些 位置 玩家 比 其他 位置 玩家 要 有 優勢 因為 他們 可以 看 其他 前面 玩家 行動 之 後 自己 再 採取 相應 行動</t>
+          <t>limit 限額 限額 下注 金額 或 下注 額 另 一個術語</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Limp（跟大盲）：在帶有盲注（強制下注）的游戲中，如果玩家將跟大盲注作為第一個動作，則表示玩家想要緩慢進行。 想要跟大盲注，不會選擇加注。</t>
+          <t>Late（後期位）：在游戲中玩家行為順序由莊家的位置決定的情況下，後期位置是指最後兩個位置（關煞位和按鈕位）。 處在這些位置的玩家比其他位置的玩家要有優勢。 因為他們可以在看了其他前面玩家的行動之後自己再採取相應的行動。</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>limp 跟大盲 帶 有 盲注 強制 下注 游戲 中 如果 玩家 將跟 大盲注 作為 第一 個動作 則 表示 玩家 想要 緩慢 進行 想要 跟 大盲注 不會 選擇 加注</t>
+          <t>late 後期位 游戲 中 玩家 行為 順序 莊家 位置 決定 情況 下 後期位 置 最後兩個 位置 關煞位 和 按鈕位 處 位置 玩家 比 其他 位置 玩家 要 有 優勢 因為 他們 可以 看 其他 前面 玩家 行動 之 後 自己 再 採取 相應 行動</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Middle（中期位）：在游戲中玩家行為順序由莊家的位置決定的情況下，中期位是指從發牌者的角度來看位於桌子中央的人。 這些位置的玩家對之後的玩家處于劣勢，面對之前的玩家 時處于有利的位置。</t>
+          <t>Limp（跟大盲）：在帶有盲注（強制下注）的游戲中，如果玩家將跟大盲注作為第一個動作，則表示玩家想要緩慢進行。 想要跟大盲注，不會選擇加注。</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>middle 中期位 游戲 中 玩家 行為 順序 莊家 位置 決定 情況 下 中期位 從 發牌者 角度 來 看位 桌子 中央 人 這些 位置 玩家 之 後 玩家 處于 劣勢 面對 之前 玩家 時處 于 有利 位置</t>
+          <t>limp 跟大盲 帶 有 盲注 強制 下注 游戲 中 如果 玩家 將跟 大盲注 作為 第一 個動作 則 表示 玩家 想要 緩慢 進行 想要 跟 大盲注 不會 選擇 加注</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Muck（棄牌區）：棄牌區指的是撲克桌上所有已使用過的紙牌放置的區域。 它包含所有洗牌卡（在某些時候將最上層的牌去掉）或玩家棄掉的牌。 棄牌區意味著不去看那些牌就放置在那。</t>
+          <t>Middle（中期位）：在游戲中玩家行為順序由莊家的位置決定的情況下，中期位是指從發牌者的角度來看位於桌子中央的人。 這些位置的玩家對之後的玩家處于劣勢，面對之前的玩家 時處于有利的位置。</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>muck 棄牌 區 棄牌 區指 撲克 桌上 所有 已 使用 過的 紙牌 放置 區域 它 包含 所有 洗牌 卡 某些 時 候將 最 上層 牌 去掉 或 玩家 棄掉 牌 棄牌 區 意味著 不去 看 那些 牌 放置 那</t>
+          <t>middle 中期位 游戲 中 玩家 行為 順序 莊家 位置 決定 情況 下 中期位 從 發牌者 角度 來 看位 桌子 中央 人 位置 玩家 之 後 玩家 處于 劣勢 面對 之前 玩家 時處 于 有利 位置</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nuts（必勝牌）：必勝牌指的是在特定情況下的最強牌。 如果在已發的牌之中，某玩家擁有最好的一手牌，那麼他就是拿到必勝牌。 </t>
+          <t>Muck（棄牌區）：棄牌區指的是撲克桌上所有已使用過的紙牌放置的區域。 它包含所有洗牌卡（在某些時候將最上層的牌去掉）或玩家棄掉的牌。 棄牌區意味著不去看那些牌就放置在那。</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>nuts 必勝牌 必勝牌 特定 情況 下 最 強牌 如果 已發 牌 之中 某 玩家 擁有 最好 一手 牌 那麼 他 就是 拿到 必勝牌</t>
+          <t>muck 棄牌 區 棄牌 區指 撲克 桌上 所有 已 使用 過的 紙牌 放置 區域 它 包含 所有 洗牌 卡 某些 時 候將 最 上層 牌 去掉 或 玩家 棄掉 牌 棄牌 區 不去 看 那些 牌 放置 那</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odds（賠率）：一定數量的聽牌，剩餘1張（可能多於1張）來牌的話就可以形成牌型並使自己的牌型增強 ，發這種牌有一定的概率。 這種概率通常稱為賠率。 </t>
+          <t xml:space="preserve">Nuts（必勝牌）：必勝牌指的是在特定情況下的最強牌。 如果在已發的牌之中，某玩家擁有最好的一手牌，那麼他就是拿到必勝牌。 </t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>odds 賠率 一定 數量 聽牌 剩餘 1 張 可能 多 1 張 來牌 話 可以 形成 牌型 並使 自己 牌型 增強 發 這種 牌 有 一定 概率 這種 概率 通常 稱為 賠率</t>
+          <t>nuts 必勝牌 必勝牌 特定 情況 下 最 強牌 如果 已發 牌 之中 某 玩家 擁有 最好 一手 牌 那麼 他 就是 拿到 必勝牌</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outs（出路）：也叫補牌，能夠使玩家在某個階段所有可能獲勝的公共牌。 </t>
+          <t xml:space="preserve">Odds（賠率）：一定數量的聽牌，剩餘1張（可能多於1張）來牌的話就可以形成牌型並使自己的牌型增強 ，發這種牌有一定的機率。 這種機率通常稱為賠率。 </t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>outs 出路 叫 補牌 能夠 使 玩家 某個 階段 所有 可能 獲勝 公共牌</t>
+          <t>odds 賠率 一定 數量 聽牌 剩餘 1 張 可能 多 1 張 來牌 話 可以 形成 牌型 並使 自己 牌型 增強 發 這種 牌 有 一定 機率 這種 機率 通常 稱為 賠率</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pocket_pair（口袋對）：在德州撲克中，口袋對是由兩個玩家的底牌組成的對子牌。 </t>
+          <t xml:space="preserve">Outs（出路）：也叫補牌，能夠使玩家在某個階段所有可能獲勝的公共牌。 </t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>pocket_pair 口袋 德州撲克 中 口袋 兩個 玩家 底牌 組成 對子 牌</t>
+          <t>outs 出路 叫 補牌 能夠 使 玩家 某個 階段 所有 可能 獲勝 公共牌</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pot（底池）：底池是一個獎池，包括在成牌過程中進行的所有下注。 </t>
+          <t xml:space="preserve">Pocket_pair（口袋對）：在德州撲克中，口袋對是由兩個玩家的底牌組成的對子牌。 </t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>pot 底池 底池 獎池 包括 成牌 過程 中 進行 所有 下注</t>
+          <t>pocket_pair 口袋 德州撲克 中 口袋 兩個 玩家 底牌 組成 對子 牌</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Pot_Limit（底池限注）：底池限制是一種「底池大小必須小於或等於當前底池大小」的下注結構。 下注可以是任何值，但必須小於或等於當前底池大小，但通常大於上次下注或加注的大小。</t>
+          <t xml:space="preserve">Pot（底池）：底池是一個獎池，包括在成牌過程中進行的所有下注。 </t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>pot_limit 底池 限注 底池 限制 一種 底池 大小 必須 小於 或 等於 當前 底池 大小 下注 結構 下注 可以 任何 值 但 必須 小於 或 等於 當前 底池 大小 但 通常 大於 上次 下注 或 加注 大小</t>
+          <t>pot 底池 底池 獎池 包括 成牌 過程 中 進行 所有 下注</t>
         </is>
       </c>
     </row>
@@ -2284,42 +2284,42 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>pot_odds（底池賠率）：底池賠率是「可以贏得的獎金」與「獲得獎金的機會所需的成本」之間的比率。 因此，它們是給定賭注的反向成本效益比。</t>
+          <t>Pot_Limit（底池限注）：底池限制是一種「底池大小必須小於或等於當前底池大小」的下注結構。 下注可以是任何值，但必須小於或等於當前底池大小，但通常大於上次下注或加注的大小。</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>pot_odds 底池 賠率 底池 賠率 可以 贏得 獎金 獲得 獎金 機會 所 需 成本 之間 比率 因此 它們 給定 賭注 反向 成本 效益 比</t>
+          <t>pot_limit 底池 限注 底池 限制 一種 底池 大小 必須 小於 或 等於 當前 底池 大小 下注 結構 下注 可以 任何 值 但 必須 小於 或 等於 當前 底池 大小 但 通常 大於 上次 下注 或 加注 大小</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Pre_flop（翻牌前）：指的是德州撲克和奧馬哈等游戲中，發出底牌後，公共牌出現以前的第一輪叫注階段。</t>
+          <t>pot_odds（底池賠率）：底池賠率是「可以贏得的獎金」與「獲得獎金的機會所需的成本」之間的比率。 因此，它們是給定賭注的反向成本效益比。</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>pre_flop 翻牌前 德州撲克 和 奧馬哈 等 游戲 中 發出 底牌 後 公共牌 出現 以前 第一 輪 叫注 階段</t>
+          <t>pot_odds 底池賠率 底池賠率 可以 贏得 獎金 獲得 獎金 機會 所 需 成本 之間 比率 因此 它們 給定 賭注 反向 成本 效益 比</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Raise（加注）：加注是當一個玩家面對另一位玩家的下注時他可以採取的動作。 加注是超過對手下注金額的下注。 每輪加注的數量和大小可能會根據每個地方的規則而受到不同限制。 通常，每輪下注允許3，4或5次（5次不常見）加注。 再次加注到對手的加注時，該加注稱為再加注。</t>
+          <t>Pre_flop（翻牌前）：指的是德州撲克和奧馬哈等游戲中，發出底牌後，公共牌出現以前的第一輪叫注階段。</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>raise 加注 加注 當一個 玩家 面對 另 一位 玩家 下注 時 他 可以 採取 動作 加注 超過 對手 下注 金額 下注 每輪 加注 數量 和 大小 可能 會 每個 地方 規則 受到 不同 限制 通常 每輪 下注 允許 3 4 或 5 次 5 次 不常見 加注 再次 加注 到 對手 加注 時 該 加注 稱為 再 加注</t>
+          <t>pre_flop 翻牌前 德州撲克 和 奧馬哈 等 游戲 中 發出 底牌 後 公共牌 出現 以前 第一 輪 叫注 階段</t>
         </is>
       </c>
     </row>
@@ -2329,27 +2329,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Re_raise（再加注）：再加注是在另一位玩家已經加注之後加注。 如果一位玩家下注，第二位玩家加注，而第三位玩家在轉牌上加注，則第三位玩家算是再加注。</t>
+          <t>Raise（加注）：加注是當一個玩家面對另一位玩家的下注時他可以採取的動作。 加注是超過對手下注金額的下注。 每輪加注的數量和大小可能會根據每個地方的規則而受到不同限制。 通常，每輪下注允許3，4或5次（5次不常見）加注。 再次加注到對手的加注時，該加注稱為再加注。</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>re_raise 再 加注 再 加注 另 一位 玩家 已經 加注 之 後 加注 如果 一位 玩家 下注 第二位 玩家 加注 第三位 玩家 轉牌 上 加注 則 第三位 玩家 算是 再 加注</t>
+          <t>raise 加注 加注 當一個 玩家 面對 另 一位 玩家 下注 時 他 可以 採取 動作 加注 超過 對手 下注 金額 下注 每輪 加注 數量 和 大小 可能 每個 地方 規則 受到 不同 限制 通常 每輪 下注 允許 3 4 或 5 次 5 次 不常見 加注 再次 加注 到 對手 加注 時 該 加注 稱為 再 加注</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>River（河牌）：德州撲克和奧馬哈等游戲中，第5張公共牌叫河牌。</t>
+          <t>Re_raise（再加注）：再加注是在另一位玩家已經加注之後加注。 如果一位玩家下注，第二位玩家加注，而第三位玩家在轉牌上加注，則第三位玩家算是再加注。</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>river 河牌 德州撲克 和 奧馬哈 等 游戲 中 第 5 張 公共牌 叫 河牌</t>
+          <t>re_raise 再 加注 再 加注 另 一位 玩家 已經 加注 之 後 加注 如果 一位 玩家 下注 第二位 玩家 加注 第三位 玩家 轉牌 上 加注 則 第三位 玩家 算是 再 加注</t>
         </is>
       </c>
     </row>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rag（廢牌）：廢牌指的是沒有價值或很弱的牌。 </t>
+          <t>River（河牌）：德州撲克和奧馬哈等游戲中，第5張公共牌叫河牌。</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>rag 廢牌 廢牌 沒 有 價值 或 很 弱 牌</t>
+          <t>river 河牌 德州撲克 和 奧馬哈 等 游戲 中 第 5 張 公共牌 叫 河牌</t>
         </is>
       </c>
     </row>
@@ -2374,72 +2374,72 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Rake（抽水）：抽水指的是每局要固定從獎池中抽取一定比例給賭場等。 如果牌局沒有進行到翻牌階段，則不會收取抽水。</t>
+          <t xml:space="preserve">Rag（廢牌）：廢牌指的是沒有價值或很弱的牌。 </t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>rake 抽水 抽水 每局 要 固定 從 獎池 中 抽取 一定 比例 給賭場 等 如果 牌局 沒有 進行 到 翻牌 階段 則不會 收取 抽水</t>
+          <t>rag 廢牌 廢牌 沒 有 價值 或 很 弱 牌</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Rock（石頭）：石頭指的是持保守態度的玩家，只有在拿到很少的幾手強牌的時候才入池。 他的策略是「只打最強的牌」，但是當拿到期望值很高的強牌時，即使很可能輸掉，也只能保持積極的態度打下去。</t>
+          <t>Rake（抽水）：抽水指的是每局要固定從獎池中抽取一定比例給賭場等。 如果牌局沒有進行到翻牌階段，則不會收取抽水。</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>rock 石頭 石頭 持 保守 態度 玩家 只有 拿到 很少 幾手 強牌 時候 才 入池 他 策略 只 打 最強 牌 但是 當 拿到 期望值 很 高 強牌 時 即使 很 可能 輸掉 只能 保持 積極 態度 打 下去</t>
+          <t>rake 抽水 抽水 每局 要 固定 從 獎池 中 抽取 一定 比例 給賭場 等 如果 牌局 沒有 進行 到 翻牌 階段 則不會 收取 抽水</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ring_game（現金桌）：現金桌是在賭場中始終開放的賭桌，您可以在這裡持籌碼坐下並以該賭桌的速度持續 玩游戲。 玩家可以自由進入游戲並站起。 如果您想以較低或較高的速度進行游戲，則必須移動桌子。</t>
+          <t>Rock（石頭）：石頭指的是持保守態度的玩家，只有在拿到很少的幾手強牌的時候才入池。 他的策略是「只打最強的牌」，但是當拿到期望值很高的強牌時，即使很可能輸掉，也只能保持積極的態度打下去。</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ring_game 現金桌 現金桌 賭場 中始 終開 放 賭桌 您 可以 這裡持 籌碼 坐下 並以 該 賭桌 速度 持續 玩游 戲 玩家 可以 自由 進入 游戲 並站 起 如果 您 想 較 低 或 較 高 速度 進行 游戲 則必須 移動 桌子</t>
+          <t>rock 石頭 石頭 持 保守 態度 玩家 只有 拿到 很少 幾手 強牌 時候 才 入池 他 策略 只 打 最強 牌 但是 拿到 期望值 很 高 強牌 時 即使 很 可能 輸掉 只能 保持 積極 態度 打 下去</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Shark（鯊魚）：鯊魚指的是桌上的強大且採取積極打法的玩家。 鯊魚攻擊弱小的玩家並從中盈利。</t>
+          <t>Ring_game（現金桌）：現金桌是在賭場中始終開放的賭桌，您可以在這裡持籌碼坐下並以該賭桌的速度持續 玩游戲。 玩家可以自由進入游戲並站起。 如果您想以較低或較高的速度進行游戲，則必須移動桌子。</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>shark 鯊魚 鯊魚 桌上 強大且 採取 積極 打法 玩家 鯊魚 攻擊 弱小 玩家 並從 中 盈利</t>
+          <t>ring_game 現金桌 現金桌 賭場 中始 終開 放 賭桌 您 可以 這裡持 籌碼 坐下 並以 該 賭桌 速度 持續 玩游 戲 玩家 可以 自由 進入 游戲 並站 起 如果 您 想 較 低 或 較 高 速度 進行 游戲 則必須 移動 桌子</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Showdown（亮牌）：亮牌是牌型（游戲）的最後部分，剩餘玩家展示自己的牌，並決定誰擁有最好的牌以及誰贏得底池。 亮牌將一樣在最後一輪下注之後進行。</t>
+          <t>Shark（鯊魚）：鯊魚指的是桌上的強大且採取積極打法的玩家。 鯊魚攻擊弱小的玩家並從中盈利。</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>showdown 亮牌 亮牌 牌型 游戲 最 後 部分 剩餘 玩家 展示 自己 牌 並決定 誰 擁有 最好 牌 誰 贏得 底池 亮牌 將一樣 最後一輪 下注 之後進行</t>
+          <t>shark 鯊魚 鯊魚 桌上 強大且 採取 積極 打法 玩家 鯊魚 攻擊 弱小 玩家 並從 中 盈利</t>
         </is>
       </c>
     </row>
@@ -2449,87 +2449,87 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Slowplay（慢打）：慢打指的是「為了使對手消除警惕，拿到強牌的時候也故意採取消極示弱的打法」，「給人以為是弱牌的印象」或「讓對手誤以 為自己拿到的是最強牌」 的戰略戰術。</t>
+          <t>Showdown（亮牌）：亮牌是牌型（游戲）的最後部分，剩餘玩家展示自己的牌，並決定誰擁有最好的牌以及誰贏得底池。 亮牌將一樣在最後一輪下注之後進行。</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>slowplay 慢打 慢打 使 對手 消除 警惕 拿到 強牌 時候 故意 採 取消 極 示弱 打法 給人以 弱牌 印象 或 讓 對手 誤以 自己 拿到 最 強牌 戰略 戰術</t>
+          <t>showdown 亮牌 亮牌 牌型 游戲 最 後 部分 剩餘 玩家 展示 自己 牌 並決定 誰 擁有 最好 牌 誰 贏得 底池 亮牌 將一樣 最後一輪 下注 之後進行</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>side_pot（邊池）：邊池是指用全押玩家的牌局中放在側面的底池。 牌局的主要底池是指所有活躍玩家都能獲得的底池。 如果一名玩家全押並且至少有兩名對手仍在賽事中並且他們不是全押，則所有隨後的下注都放在邊池中，而不是全押的玩家可以獲得。</t>
+          <t>Slowplay（慢打）：慢打指的是「為了使對手消除警惕，拿到強牌的時候也故意採取消極示弱的打法」，「給人以為是弱牌的印象」或「讓對手誤以 為自己拿到的是最強牌」 的戰略戰術。</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>side_pot 邊池 邊池 指用 全押 玩家 牌局 中 放在 側面 底池 牌局 主要 底池 所有 活躍 玩家 能 獲得 底池 如果 一名 玩家 全押 並且 至少 有 兩名 對手 仍 賽事 中 並且 他們 不是 全押 則 所有 隨後的 下注 放在 邊池 中 不是 全押 玩家 可以 獲得</t>
+          <t>slowplay 慢打 慢打 使 對手 消除 警惕 拿到 強牌 時候 故意 採 取消 極 示弱 打法 給人以 弱牌 印象 或 讓 對手 誤以 自己 拿到 最 強牌 戰略 戰術</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Semi_bluff（半詐牌）：半詐牌指的是用目前較弱但有可能發展成強牌的手牌進行虛張聲勢。 半詐牌的目標不一定是淘汰所有對手。 因為如果在亮牌為止完成牌型，仍然有機會獲得底池。 因此，半詐牌的目的之一是在早期下注中將籌碼盡可能收集到底池中，以增加可能獲得的籌碼。 這一舉動是有益的，因為對手很可能棄牌並且自己可能可以贏得一個大底池。 半詐牌適用的典型情況是當自己在聽牌的時候，如果發出了適當的牌，將很可能形成牌型。</t>
+          <t>side_pot（邊池）：邊池是指用全押玩家的牌局中放在側面的底池。 牌局的主要底池是指所有活躍玩家都能獲得的底池。 如果一名玩家全押並且至少有兩名對手仍在賽事中並且他們不是全押，則所有隨後的下注都放在邊池中，而不是全押的玩家可以獲得。</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>semi_bluff 半詐牌 半詐牌 用 目前 較弱 但 有 可能 發展 成 強牌 手牌 進行 虛張 聲勢 半詐牌 目標 不 一定 淘汰 所有 對手 因為 如果 亮牌 為止 完成 牌型 仍然 有 機會 獲得 底池 因此 半詐牌 目的 之一 早期 下注 中將 籌碼 盡 可能 收集 到底 池中 增加 可能 獲得 籌碼 這一 舉動 有益 因為 對手 很 可能 棄牌 並且 自己 可能 可以 贏得 大底 池 半詐牌 適用 典型 情況 是當 自己 聽牌 時候 如果 發出 適當 牌 將 很 可能 形成 牌型</t>
+          <t>side_pot 邊池 邊池 指用 全押 玩家 牌局 中 放在 側面 底池 牌局 主要 底池 所有 活躍 玩家 能 獲得 底池 如果 一名 玩家 全押 並且 至少 有 兩名 對手 仍 賽事 中 並且 他們 不是 全押 則 所有 隨後的 下注 放在 邊池 中 不是 全押 玩家 可以 獲得</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Starting_hand_chat（起始手牌表）：起始手牌表是可以入池的手牌的概率表格歸納，並說明瞭根據這些手要採取的操作。 SHC（起始手牌表）對于初學者在第一輪下注中制定策略特別有用。</t>
+          <t>Semi_bluff（半詐牌）：半詐牌指的是用目前較弱但有可能發展成強牌的手牌進行虛張聲勢。 半詐牌的目標不一定是淘汰所有對手。 因為如果在亮牌為止完成牌型，仍然有機會獲得底池。 因此，半詐牌的目的之一是在早期下注中將籌碼盡可能收集到底池中，以增加可能獲得的籌碼。 這一舉動是有益的，因為對手很可能棄牌並且自己可能可以贏得一個大底池。 半詐牌適用的典型情況是當自己在聽牌的時候，如果發出了適當的牌，將很可能形成牌型。</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>starting_hand_chat 起始 手牌表 起始 手牌 表是 可以 入池 手牌 概率 表格 歸納 並說明 瞭根據 這些 手要 採取 操作 shc 起始 手牌表 對于 初學者 第一 輪 下注 中 制定 策略 特別 有用</t>
+          <t>semi_bluff 半詐牌 半詐牌 用 目前 較弱 但 有 可能 發展 成 強牌 手牌 進行 虛張 聲勢 半詐牌 目標 不 一定 淘汰 所有 對手 因為 如果 亮牌 為止 完成 牌型 仍然 有 機會 獲得 底池 因此 半詐牌 目的 之一 早期 下注 中將 籌碼 盡 可能 收集 到底 池中 增加 可能 獲得 籌碼 這一 舉動 有益 因為 對手 很 可能 棄牌 並且 自己 可能 可以 贏得 大底 池 半詐牌 適用 典型 情況 是當 自己 聽牌 時候 如果 發出 適當 牌 將 很 可能 形成 牌型</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Streak（連運）：連運指的是牌局中連著幸運贏牌或連著厄運輸牌的情況。</t>
+          <t>Starting_hand_chat（起始手牌表）：起始手牌表是可以入池的手牌的機率表格歸納，並說明瞭根據這些手要採取的操作。 SHC（起始手牌表）對于初學者在第一輪下注中制定策略特別有用。</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>streak 連運 連運指 牌局 中連著 幸運 贏牌 或 連著 厄 運輸牌 情況</t>
+          <t>starting_hand_chat 起始 手牌表 起始 手牌 表是 可以 入池 手牌 機率 表格 歸納 並說明 瞭根據 手要 採取 操作 shc 起始 手牌表 對于 初學者 第一 輪 下注 中 制定 策略 特別 有用</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Turn（轉牌）：德州撲克或奧馬哈等有使用公共牌的游戲中，第4張公共牌稱作轉牌。</t>
+          <t>Streak（連運）：連運指的是牌局中連著幸運贏牌或連著厄運輸牌的情況。</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>turn 轉牌 德州撲克 或 奧馬哈 等 有 使用 公共牌 游戲 中 第 4 張 公共牌 稱作 轉牌</t>
+          <t>streak 連運 連運指 牌局 中連著 幸運 贏牌 或 連著 厄 運輸牌 情況</t>
         </is>
       </c>
     </row>
@@ -2539,72 +2539,72 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Tell（小動作）：小動作是指玩家無意間透露出來的一些下意識的動作，這些動作有可能讓他輸掉。 其中也包括有意識的動作。 比如發現對方正在觀察自己的時候刻意作出一些假動作演技讓對手作出錯誤判斷。</t>
+          <t>Turn（轉牌）：德州撲克或奧馬哈等有使用公共牌的游戲中，第4張公共牌稱作轉牌。</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>tell 小動作 小動作 玩家 無意間 透露 出來 一些 下意識 動作 這些 動作 有 可能 讓 他 輸掉 其中 包括 有意 識 動作 比如 發現 方正 觀察 自己 時候 刻意 作出 一些 假動作 演技 讓 對手 作出 錯誤 判斷</t>
+          <t>turn 轉牌 德州撲克 或 奧馬哈 等 有 使用 公共牌 游戲 中 第 4 張 公共牌 稱作 轉牌</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tilt（上頭）：上頭指的是指玩家無法做出合理判斷，出現了一些情緒化的狀態。 </t>
+          <t>Tell（小動作）：小動作是指玩家無意間透露出來的一些下意識的動作，這些動作有可能讓他輸掉。 其中也包括有意識的動作。 比如發現對方正在觀察自己的時候刻意作出一些假動作演技讓對手作出錯誤判斷。</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>tilt 上頭 上頭 玩家 無法 做出 合理 判斷 出現 一些 情緒化 狀態</t>
+          <t>tell 小動作 小動作 玩家 無意間 透露 出來 一些 下意識 動作 動作 有 可能 讓 他 輸掉 其中 包括 有意 識 動作 比如 發現 方正 觀察 自己 時候 刻意 作出 一些 假動作 演技 讓 對手 作出 錯誤 判斷</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Tournament（賽事）：撲克賽事是一種游戲形式，每個玩家都可以通過買入來參加賽事。 每個玩家最初獲得相同數量的籌碼，如果輸掉了手上所有籌碼，就輸掉了賽事。 在可重購的賽事中，玩家可以在初始階段再次買入。 獎金是根據贏得賽事的玩家的排名分配的。 根據特定的支出結構，確定獲得多少獎金。 當然，可以使用金錢以外的獎品。</t>
+          <t xml:space="preserve">Tilt（上頭）：上頭指的是指玩家無法做出合理判斷，出現了一些情緒化的狀態。 </t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>tournament 賽事 撲克賽 事 一種 游戲 形式 每個 玩家 可以 通過 買入 來 參加賽 事 每個 玩家 最初 獲得 相同 數量 籌碼 如果 輸掉 手上 所有 籌碼 輸掉 賽事 可 重購 賽事 中 玩家 可以 初始 階段 再次 買入 獎金 贏得賽 事 玩家 排名 分配 特定 支出 結構 確定 獲得 多少 獎金 當然 可以 使用 金錢 以外 獎品</t>
+          <t>tilt 上頭 上頭 玩家 無法 做出 合理 判斷 出現 一些 情緒化 狀態</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>UTG(Under_the_Gun)（槍口位）：大盲注左手邊第一個為槍口位，翻牌前最先行動，在德州撲克裡位置越靠後越有利，因此坐在槍口位的玩家是最被動的玩家，由於起手牌要求比其他位置都要高，往往會翻牌前棄牌。</t>
+          <t>Tournament（賽事）：撲克賽事是一種游戲形式，每個玩家都可以通過買入來參加賽事。 每個玩家最初獲得相同數量的籌碼，如果輸掉了手上所有籌碼，就輸掉了賽事。 在可重購的賽事中，玩家可以在初始階段再次買入。 獎金是根據贏得賽事的玩家的排名分配的。 根據特定的支出結構，確定獲得多少獎金。 當然，可以使用金錢以外的獎品。</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>utg under_the_gun 槍口位 大盲注 左手 邊 第一 個 槍口位 翻牌前 最先 行動 德州撲克 裡 位置 越靠後越 有利 因此 坐在 槍口位 玩家 最 動 玩家 起 手牌 要求 比 其他 位置 要 高 往往 會 翻牌前 棄牌</t>
+          <t>tournament 賽事 撲克賽 事 一種 游戲 形式 每個 玩家 可以 通過 買入 來 參加賽 事 每個 玩家 最初 獲得 相同 數量 籌碼 如果 輸掉 手上 所有 籌碼 輸掉 賽事 可 重購 賽事 中 玩家 可以 初始 階段 再次 買入 獎金 贏得賽 事 玩家 排名 分配 特定 支出 結構 確定 獲得 多少 獎金 當然 可以 使用 金錢 以外 獎品</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>概率與賠率的基本概念：概率是自己擊中公共牌後能贏的機率；賠率是投入籌碼和贏回籌碼之間的比例。打牌不算概率幾乎是在瞎玩，概率和賠率就是幫你做正確決定的工具。</t>
+          <t>UTG(Under_the_Gun)（槍口位）：大盲注左手邊第一個為槍口位，翻牌前最先行動，在德州撲克裡位置越靠後越有利，因此坐在槍口位的玩家是最被動的玩家，由於起手牌要求比其他位置都要高，往往會翻牌前棄牌。</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>概率 賠率 基本概念 概率 自己 擊中 公共牌 後 能贏 機率 賠率 投入 籌碼 和 贏回 籌碼 之間 比例 打牌 不算 概率 幾乎 瞎 玩 概率 和 賠率 就是 幫 你 做 正確 決定 工具</t>
+          <t>utg under_the_gun 槍口位 大盲注 左手 邊 第一 個 槍口位 翻牌前 最先 行動 德州撲克 裡 位置 越靠後越 有利 因此 坐在 槍口位 玩家 最 動 玩家 起 手牌 要求 比 其他 位置 要 高 往往 翻牌前 棄牌</t>
         </is>
       </c>
     </row>
@@ -2614,42 +2614,42 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Outs (出路) 與2與4法則：數能贏的牌叫做 Outs（出路）。算概率。簡單算法是2與4法則：在發出翻牌之後，能贏的概率是用你能贏的牌的張數乘以 4；在轉牌後，用你能贏的數量乘以 2。這是因為未知的牌大約剩 50 張左右所換算出的百分比捷徑。</t>
+          <t>補牌陷阱，有時候我們的補牌的確會讓我們成為更強的牌型，但卻同時讓對手成為「更強」的牌型，這時候我們通常會把這些補牌數稱作「不乾淨的Outs」</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>outs 出路 2與4法則 數能贏 牌 叫做 outs 出路 算 概率 簡單 算法 2與4法則 發出 翻牌 之 後 能贏 概率 用 你 能贏 牌 張數 乘以 4 轉牌 後 用 你 能贏 數量 乘以 2 這是 因為 未知 牌大約 剩 50 張 左右 所換 算出 百分比 捷徑</t>
+          <t>補牌 陷阱 有 時候 我們 補牌 確會 讓 我們 成為 更強 牌型 但 卻 同時 讓 對手 成為 更強 牌型 我們 通常 補牌 數稱 作 不乾淨 outs</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>賠率計算與決策應用：賠率是你要付出的籌碼和已經在底池裡籌碼的比例。拿賠率對比算出來的概率，如果贏的概率高於投入的賠率，數學上就應該跟注；反之則棄牌。</t>
+          <t>機率與賠率的基本概念：機率是自己擊中公共牌後能贏的機率；賠率是投入籌碼和贏回籌碼之間的比例。打牌不算機率幾乎是在瞎玩，機率和賠率就是幫你做正確決定的工具。</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>賠率 計算 決策 應用 賠率 你 要 付出 籌碼 和 已經 底 池裡 籌碼 比例 拿 賠率 比算 出來 概率 如果 贏的 概率 高 投入 賠率 數學 上 應該 跟注 反之 則 棄牌</t>
+          <t>機率 賠率 基本概念 機率 自己 擊中 公共牌 後 能贏 機率 賠率 投入 籌碼 和 贏回 籌碼 之間 比例 打牌 不算 機率 幾乎 瞎 玩 機率 和 賠率 就是 幫 你 做 正確 決定 工具</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>隱含賠率 (Implied_Odds)：當單算賠率不足以跟注時，需考慮對手後手的籌碼。當你確定發出你要的牌（中牌）後，對手會支付他後手還不在底池裡的籌碼時，就可以把這些籌碼預先算入你能贏的底池中來重新計算賠率。這通常適用於對手牌力極強而難以棄牌的情況。</t>
+          <t>Outs (出路、補牌) 與2與4法則：數能贏的牌叫做 Outs（出路、補牌）。算機率。簡單算法是2與4法則：在發出翻牌之後，能贏的機率是用你能贏的牌的張數乘以 4；在轉牌後，用你能贏的數量乘以 2。這是因為未知的牌大約剩 50 張左右所換算出的百分比捷徑。</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>隱含 賠率 implied_odds 當單 算 賠率 不足以 跟注 時 需考慮 對手 後 手 籌碼 當你 確定 發出 你 要 牌 中牌 後 對手 會 支付 他後手 還不在 底 池裡 籌碼 時 可以 把 這些 籌碼 預先 算入 你 能贏 底池 中來 重新 計算 賠率 這 通常 適用 對手 牌力 極強 難以 棄牌 情況</t>
+          <t>outs 出路 補牌 2與4法則 數能贏 牌 叫做 outs 出路 補牌 算 機率 簡單 算法 2與4法則 發出 翻牌 之 後 能贏 機率 用 你 能贏 牌 張數 乘以 4 轉牌 後 用 你 能贏 數量 乘以 2 這是 因為 未知 牌大約 剩 50 張 左右 所換 算出 百分比 捷徑</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>棄牌率 (Fold_Equity)：即使目前牌力落後，但透過再加注等激進打法，讓對手覺得自己牌力不夠大而選擇蓋牌的機率。打棄牌率對於玩家的讀牌能力有一定要求，讀對手牌力範圍越準，就越能找到詐唬（偷雞）的時機。</t>
+          <t>賠率計算與決策應用：賠率是你要付出的籌碼和已經在底池裡籌碼的比例。拿賠率對比算出來的機率，如果贏的機率高於投入的賠率，數學上就應該跟注；反之則棄牌。</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>棄牌 率 fold_equity 即使 目前 牌力 落 後 但 透過 再 加注 等 激進 打法 讓 對手 覺得 自己 牌力 不夠 大 選擇 蓋牌 機率 打 棄牌 率 玩家 讀牌 能力 有 一定 要求 讀 對手 牌力 範圍 越準 越 能 找到 詐唬 偷雞 時機</t>
+          <t>賠率 計算 決策 應用 賠率 你 要 付出 籌碼 和 已經 底 池裡 籌碼 比例 拿 賠率 比算 出來 機率 如果 贏的 機率 高 投入 賠率 數學 上 應該 跟注 反之 則 棄牌</t>
         </is>
       </c>
     </row>
@@ -2674,72 +2674,177 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>範圍與範圍優勢：在撲克對抗中，範圍是不可忽略的因素。翻牌前在前位（如槍口位 UTG）加注（Raise）的人，通常會被認為牌力範圍很強（例如範圍內包含最大的同花 A）。玩家可以有效地利用自己的範圍優勢來進行詐唬（偷雞），前提是對手也具備解讀範圍的能力。</t>
+          <t>隱含賠率 (Implied_Odds)：當單算賠率不足以跟注時，需考慮對手後手的籌碼。當你確定發出你要的牌（中牌）後，對手會支付他後手還不在底池裡的籌碼時，就可以把這些籌碼預先算入你能贏的底池中來重新計算賠率。這通常適用於對手牌力極強而難以棄牌的情況。</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>範圍 範圍 優勢 撲克 抗中 範圍 不可 忽略 因素 翻牌前 前位 如 槍口位 utg 加注 raise 人 通常 會 認為 牌力 範圍 很強 例如 範圍 內 包含 最大 同花 a 玩家 可以 有效 地 利用 自己 範圍 優勢 來 進行 詐唬 偷雞 前提 對手 具備 解讀 範圍 能力</t>
+          <t>隱含 賠率 implied_odds 當單 算 賠率 不足以 跟注 時 需考慮 對手 後 手 籌碼 當你 確定 發出 你 要 牌 中牌 後 對手 支付 他後手 還不在 底 池裡 籌碼 時 可以 籌碼 預先 算入 你 能贏 底池 中來 重新 計算 賠率 通常 適用 對手 牌力 極強 難以 棄牌 情況</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>翻牌前動作與範圍判斷：翻牌前起 Raise 的人，其範圍是「無上限」的（包含 AA、KK 等）。相反地，面對加注卻只是選擇跟注（沒有 3bet）的玩家，通常會被認為排除了最頂級的牌力，範圍主要集中在中等牌力，因為拿大牌通常會選擇 3bet 來避免給後面玩家太好的賠率。</t>
+          <t>棄牌率 (Fold_Equity)：即使目前牌力落後，但透過再加注等激進打法，讓對手覺得自己牌力不夠大而選擇蓋牌的機率。打棄牌率對於玩家的讀牌能力有一定要求，讀對手牌力範圍越準，就越能找到詐唬（偷雞）的時機。</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>翻牌前 動作 範圍 判斷 翻牌前 起 raise 人 其範圍 無 上限 包含 aa kk 等 相反 地 面對 加注 卻 只是 選擇 跟注 沒有 3bet 玩家 通常 會 認為 排除 最 頂級 牌力 範圍 主要 集中 中等 牌力 因為 拿 大牌 通常 會選擇 3bet 來 避免 給後面 玩家 太好 賠率</t>
+          <t>棄牌 率 fold_equity 即使 目前 牌力 落 後 但 透過 再 加注 等 激進 打法 讓 對手 覺得 自己 牌力 不夠 大 選擇 蓋牌 機率 打 棄牌 率 玩家 讀牌 能力 有 一定 要求 讀 對手 牌力 範圍 越準 越 能 找到 詐唬 偷雞 時機</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>3bet 的作用與好處：當拿到一、二等強牌時，面對前位加注強烈建議進行 3bet。好處包含：利用位置優勢搶奪主動權，讓翻牌後更容易打；把自己的範圍擴大並維持在最高範圍；隔離後面牌力較弱的玩家入池。</t>
+          <t>範圍與範圍優勢：在撲克對抗中，範圍是不可忽略的因素。翻牌前在前位（如槍口位 UTG）加注（Raise）的人，通常會被認為牌力範圍很強（例如範圍內包含最大的同花 A）。玩家可以有效地利用自己的範圍優勢來進行詐唬（偷雞），前提是對手也具備解讀範圍的能力。</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3bet 作用 好 處 當 拿到 一 二等 強牌 時 面對 前位 加注 強烈 建議 進行 3bet 好處 包含 利用 位置 優勢 搶 奪主動權 讓 翻牌後 更 容易 打 把 自己 範圍 擴大 並維持 最高 範圍 隔離後面 牌力 較 弱 玩家 入池</t>
+          <t>範圍 範圍 優勢 撲克 抗中 範圍 不可 忽略 因素 翻牌前 前位 如 槍口位 utg 加注 raise 人 通常 認為 牌力 範圍 很強 例如 範圍 內 包含 最大 同花 a 玩家 可以 有效 地 利用 自己 範圍 優勢 來 進行 詐唬 偷雞 前提 對手 具備 解讀 範圍 能力</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>大盲位的底端範圍：當翻牌前已有多人入池，大盲位玩家因為擁有極佳的賠率而選擇最後跟注時，其範圍通常沒有頂端牌力（否則會選擇加注），但包含了極廣的「底端範圍」（各種小牌）。因此，當翻牌發出如 4、5、6 這類小牌面時，大盲位反而是最有可能擊中牌面的人。</t>
+          <t>翻牌前動作與範圍判斷：翻牌前起 Raise 的人，其範圍是「無上限」的（包含 AA、KK 等）。相反地，面對加注卻只是選擇跟注（沒有 3bet）的玩家，通常會被認為排除了最頂級的牌力，範圍主要集中在中等牌力，因為拿大牌通常會選擇 3bet 來避免給後面玩家太好的賠率。</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>大盲位 底端 範圍 當 翻牌前 已有 多人入 池 大盲位 玩家 因為 擁有 極佳 賠率 選擇 最 後 跟注 時 其範圍 通常 沒有 頂端 牌力 否則 會 選擇 加注 但 包含 極廣 底端 範圍 各種 小牌 因此 當 翻牌 發出 如 4 5 6 這類 小牌 面時 大盲位 反而 最 有 可能 擊中 牌面 人</t>
+          <t>翻牌前 動作 範圍 判斷 翻牌前 起 raise 人 其 範圍 無 上限 包含 aa kk 等 相反 地 面對 加注 卻 只是 選擇 跟注 沒有 3bet 玩家 通常 認為 排除 最 頂級 牌力 範圍 主要 集中 中等 牌力 因為 拿 大牌 通常 會選擇 3bet 來 避免 給後面 玩家 太好 賠率</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
+          <t>3bet 的作用與好處：當拿到一、二等強牌時，面對前位加注強烈建議進行 3bet。好處包含：利用位置優勢搶奪主動權，讓翻牌後更容易打；把自己的範圍擴大並維持在最高範圍；隔離後面牌力較弱的玩家入池。</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>3bet 作用 好 處 拿到 一 二等 強牌 時 面對 前位 加注 強烈 建議 進行 3bet 好處 包含 利用 位置 優勢 搶 奪主動權 讓 翻牌後 更 容易 打 自己 範圍 擴大 並維持 最高 範圍 隔離後面 牌力 較 弱 玩家 入池</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>3</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>大盲位的底端範圍：當翻牌前已有多人入池，大盲位玩家因為擁有極佳的賠率而選擇最後跟注時，其範圍通常沒有頂端牌力（否則會選擇加注），但包含了極廣的「底端範圍」（各種小牌）。因此，當翻牌發出如 4、5、6 這類小牌面時，大盲位反而是最有可能擊中牌面的人。</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>大盲位 底端 範圍 翻牌前 已有 多人入 池 大盲位 玩家 因為 擁有 極佳 賠率 選擇 最 後 跟注 時 其 範圍 通常 沒有 頂端 牌力 否則 選擇 加注 但 包含 極廣 底端 範圍 各種 小牌 因此 翻牌 發出 如 4 5 6 這類 小牌 面時 大盲位 反而 最 有 可能 擊中 牌面 人</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>0</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
           <t>形象 (Image) 對詐唬的影響：偷雞能否成功，除了合理的範圍建構外，「形象」也是關鍵因素。如果玩家平時打法非常兇且具創造性，對手較容易去抓他的詐唬；但如果是同樣的範圍操作換成形象不同的玩家來打，對手極可能就會選擇棄牌。</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>形象 image 詐唬 影響 偷雞 能否 成功 除了 合理 範圍 建構 外 形象 關鍵 因素 如果 玩家 平時 打法 非常 兇且 具創 造性 對手 較 容易 去 抓 他 詐唬 但 如果 同樣 範圍 操作 換成 形象 不同 玩家 來 打 對手 極 可能 就會 選擇 棄牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>4</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>在河牌圈面對對手的重注時，決定是否抓雞不能只憑感覺。當你手持中等牌力，也就是只能贏過對手詐唬的牌型時，必須計算底池賠率。對手是是滿池下注比起對手下注半個底池，你會需要更高的勝率</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>河牌圈 面對 對手 重注 時 決定 是否 抓雞 不能 只 憑 感覺 當你 手持 中等 牌力 就是 只能 贏過 對手 詐唬 牌型 時 必須 計算 底池賠率 對手 滿池 下注 比起 對手 下注 半個 底池 你 需要 更 高 勝率</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>0</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>當對手在河牌下達超池重注時，他們的範圍通常是極化的。這意味著對手不是持有絕對的堅果強牌，就是純粹的空氣牌在詐唬，幾乎不會有中等牌力。面對極化範圍，你的頂對或是第三大對子的牌力價值是完全一樣的，這時候你的決策應該完全基於對手的詐唬頻率與你的阻擋牌效應。</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>對手 河牌 下達 超池 重注 時 他們 範圍 通常 極化 對手 不是 持有 絕對 堅果 強牌 就是 純粹 空氣牌 詐唬 幾乎 不會 有 中等 牌力 面對 極化 範圍 你 頂 或是 第三 大 對子 牌力 價值 完全 一樣 你 決策 應該 完全 基 對手 詐唬 頻率 你 阻擋牌效應</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>1</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>最低防守頻率是防止對手利用任意兩張牌對你進行無腦詐唬的數學模型。計算公式為底池大小除以底池大小與對手下注大小的總和。</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>最低防守頻率 防止 對手 利用 任意 兩張牌 你 進行 無腦 詐唬 數學 模型 計算 公式 底池 大小 除以 底池 大小 對手 下注 大小 總 和</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>4</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>在河牌面臨大注猶豫是否抓雞時，阻擋牌是關鍵的決策依據。如果你手上的底牌包含了破壞對手堅果牌組合的關鍵牌，對手在詐唬的機率相對提升。</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>河牌 面臨 大注 猶豫 是否 抓雞 時 阻擋牌 關鍵 決策 依據 如果 你 手上 底牌 包含 破壞 對手 堅果 牌 組合 關鍵牌 對手 詐唬 機率 相對 提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>0</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>每個玩家在遊戲樹的任何決策點都會帶著一手牌的範圍。當你在特定位置的特定手牌，有一張牌與你對手的範圍相關時，那張牌就被認為是「阻擋牌」。它之所以被稱為阻擋牌，是因為它會讓你的對手更有可能或更不可能持有某種牌。</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>每個 玩家 遊戲 樹 任何 決策點 帶 著 一手 牌 範圍 當你 特定 位置 特定 手牌 有 一 張牌 你 對手 範圍 相關 時 那 張牌 認為 阻擋牌 它 之所以 稱 阻擋牌 因為 它 讓 你 對手 更 有 可能 或 更 不 可能 持有 某種 牌</t>
         </is>
       </c>
     </row>

--- a/data/分群結果.xlsx
+++ b/data/分群結果.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C162"/>
+  <dimension ref="A1:C194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,7 +435,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -450,7 +450,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -465,7 +465,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -480,7 +480,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -495,7 +495,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -525,7 +525,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -2604,13 +2604,13 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>utg under_the_gun 槍口位 大盲注 左手 邊 第一 個 槍口位 翻牌前 最先 行動 德州撲克 裡 位置 越靠後越 有利 因此 坐在 槍口位 玩家 最 動 玩家 起 手牌 要求 比 其他 位置 要 高 往往 翻牌前 棄牌</t>
+          <t>utg under_the_gun 槍口位 大盲注 左手 邊 第一 個 槍口位 翻牌前 最先 行動 德州撲克 裡 位置 越靠後越 有利 因此 坐在 槍口位 玩家 最 動 玩家 起手牌 要求 比 其他 位置 要 高 往往 翻牌前 棄牌</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -2845,6 +2845,486 @@
       <c r="C162" t="inlineStr">
         <is>
           <t>每個 玩家 遊戲 樹 任何 決策點 帶 著 一手 牌 範圍 當你 特定 位置 特定 手牌 有 一 張牌 你 對手 範圍 相關 時 那 張牌 認為 阻擋牌 它 之所以 稱 阻擋牌 因為 它 讓 你 對手 更 有 可能 或 更 不 可能 持有 某種 牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>4</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>開局加注該下多少？常見的標準開局加注是 2 到 3 個大盲(BB)。線上多用 2~2.5 BB，實體現場多用 3 BB。若前面已有人只跟大盲(limp)進場，通常每多一個 limper 就多加 1 BB。</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>開局 加注 該下 多少 ？ 常見 標準 開局 加注 2 到 3 個大盲 bb 線上 多用 2 ~ 2.5 bb 實體 現場 多用 3 bb 前面 已有 人 只 跟 大盲 limp 進場 通常 每多 limper 多加 1 bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>0</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>持續下注(c_bet)要下多大？翻牌後第一槍通常下底池的三分之一到三分之二。對手不容易聽牌可以下小，約 1/3 底池；很多同花、順子聽牌就下大一點，約 2/3 到 3/4 底池施壓。</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>持續下注 c_bet 要 下 多 大 ？ 翻牌後 第一 槍 通常 下底 池 三分之一 到 三分之二 對手 不 容易 聽牌 可以 下 小 約 1 3 底池 很多 同花 順子 聽牌 下 大 一點 約 2 3 到 3 4 底池 施壓</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>1</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>下注大小要用「底池的幾分之幾」來想，而不是固定幾個籌碼。用相對底池的概念，才能在不同底池大小下都做出合理的下注。</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>下注 大小 要 用 底池 幾分 之 幾 來 想 不是 固定 幾個 籌碼 用 相 底池 概念 才能 不同 底池 大小 下 做出 合理 下注</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>4</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>翻牌前再加注(3bet)該下多少？面對對手的開局加注，新手可以簡化成原加注額的 3 到 4 倍。位置好可下小一點，位置差(在對手前面行動)就下大一點來保護。</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>翻牌前 再 加注 3bet 該下 多少 ？ 面對 對手 開局 加注 新手 可以 簡 化成 原 加注 額 3 到 4 倍 位置 好 可下 小 一點 位置 差 對手 前面 行動 下 大 一點 來 保護</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>0</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>新手常見的下注尺寸錯誤：價值大牌時下很大、詐唬時下很小，這會讓觀察力好的對手一眼看穿你的牌力。應該讓相同情境下的下注大小盡量一致。</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>新手 常見 下注 尺寸 錯誤 價值 大牌 時下 很大 詐唬 時下 很小 這會 讓 觀察力 好 對手 一眼看穿 你 牌力 應該 讓 相同 情境 下 下注 大小 盡量 一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>0</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>下注太小的問題：在大底池只下一點點，等於送給對手很好的賠率去追聽牌。想要保護成手牌或施壓，就要下到足夠的大小。</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>下注 太小 問題 大底 池 只 下 一點點 等於 送給 對手 很 好 賠率 去 追 聽牌 想要 保護成 手牌 或 施壓 就要 下到 足夠 大小</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>0</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>什麼是價值下注？價值下注是指你覺得自己的手牌是領先的，因此下注是為了從對手那裡「榨取更多籌碼」，下注金額不能太大，否則會嚇跑對手</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>什麼 價值 下注 ？ 價值 下注 你 覺得 自己 手牌 領先 因此 下注 從 對手 那裡 榨取 更多 籌碼 下注 金額 不能 太 大 否則 會嚇 跑 對手</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>0</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>下注是你在遊戲中唯一能主動發聲的方式，所以才會有這麼多種下注策略。每一種下注金額、時機、方式，其實都是在告訴對手一個訊息，也是在試圖引導他們做出你希望的反應。不同情況，需要不同目的的下注，增加不可預測性，讓對手無法掌握你的節奏</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>下注 你 遊戲 中 唯一 能主動 發聲 方式 所以 才 有 這麼 多種 下注 策略 每一種 下注 金額 時機 方式 其實 告訴 對手 訊息 試圖 引導 他們 做出 你 希望 反應 不 同情 況 需要 不同 目的 下注 增加 不可 預測性 讓 對手 無法 掌握 你 節奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>1</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>輪到你才行動。在還沒輪到你的時候就先表態、先亮牌或先把牌丟出去，會洩漏資訊、影響其他玩家的決定，是牌桌上的大忌。</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>你 才 行動 還沒輪 到 你 時候 先表態 先 亮牌 或 先 牌 丟 出去 會洩漏 資訊 影響 其他 玩家 決定 牌 桌上 大忌</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>4</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>下注時請一次把籌碼放到下注線前，不要分好幾次把籌碼一點一點推出去，分次推注通常不被允許，只會算第一次的金額。</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>下注 時請 一次 籌碼 放到 下注 線前 不要 分好 幾次 籌碼 一點 一點 推出 去 分 次 推注 通常 不 允許 只會算 第一次 金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>0</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>還沒攤牌前，不要評論正在進行的這手牌，也不要把你已蓋掉的牌內容說出來。討論進行中的牌局會影響仍在牌局裡的玩家，屬於違規行為。</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>還沒攤 牌前 不要 評論 正在 進行 這手牌 不要 你 已 蓋 掉 牌 內容 說 出來 討論 進行 中 牌局 影響 仍 牌局 裡的 玩家 屬 違規行</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>1</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>保護好你的底牌：用一個籌碼或專用牌蓋壓在牌上，避免荷官誤收或和別人的棄牌混在一起。一旦底牌碰到棄牌堆，這手牌通常就作廢了。</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>保護 好 你 底牌 用 籌碼 或 專用 牌蓋壓 牌 上 避免 荷官 誤收 或 和 別人 棄牌 混在 一起 一旦 底牌 碰到 棄牌 堆 這手牌 通常 就作 廢</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>1</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>不要對其他玩家的打法指指點點或當場教學，也不要催促別人快點行動。給每位玩家合理的思考時間，是基本的尊重。</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>不要 其他 玩家 打法 指指 點點 或 當場 教學 不要 催促 別人 快點 行動 給 每位 玩家 合理 思考 時間 基本 尊重</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>0</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>該帶多少錢上桌？現金桌只帶你「願意輸掉」的金額，絕對不要帶上全部身家或生活費。把撲克的資金和日常生活開銷完全分開。</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>該 帶 多少 錢 上桌 ？ 現金桌 只 帶 你 願意 輸掉 金額 絕對 不要 帶上 全部 身家 或 生活 費 撲克 資金 和 日常生活 開銷 完全 分開</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>0</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>資金管理的常見原則：玩現金桌時，準備約 20 到 30 個買入的總資金，這樣即使連續輸幾局，也不會一次就破產出局。</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>資金 管理 常見 原則 玩現 金桌 時 準備 約 20 到 30 個 買入 總資金 這樣 即使 連續 輸幾局 不會 一次 破產 出局</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>0</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>選擇適合自己資金的盲注級別，不要越級挑戰高盲注的桌。級別越高、對手越強、波動越大，新手應該從小級別開始累積經驗與資金。</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>選擇 適合 自己 資金 盲注 級別 不要 越級 挑戰高 盲注 桌 級別 越 高 對手 越強 波動 越大 新手 應該 從 小級別 開始 累積 經驗 資金</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>0</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>設定停損點：給自己定一個「今天輸到多少就離桌」的金額。輸牌後容易情緒化追損(上頭)，事先設好停損能保護你的資金與心態。</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>設定 停 損點 給 自己 定一個 今天 輸到 多少 離桌 金額 輸牌 後 容易 情緒化 追損 上頭 事先 設好 停 損能 保護 你 資金 心態</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>0</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>錦標賽的資金需求比現金桌更高。因為錦標賽名次波動(方差)很大，常常要打很多場才會中獎，建議單場買入只占總資金更小的比例。</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>錦標賽 資金 需求 比現 金桌 更 高 因為 錦 標賽 名次 波動 方差 很大 常常 要 打 很多 場才會 中獎 建議 單場 買入 只 占 總資金 更 小 比例</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>4</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>哪些起手牌一定能玩？大對子 AA、KK、QQ、JJ，以及 AK、AQ 這類強牌，在任何位置幾乎都可以加注進場，是新手最安全的選擇。</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>哪些 起手牌 一定 能 玩 ？ 大 對子 aa kk qq jj ak aq 這類 強牌 任何 位置 幾乎 可以 加注 進場 新手 最 安全 選擇</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>0</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>新手可以玩的中等起手牌：中小對子(例如 99、88、77)、同花的 A(如 A5s)、以及同花連張(如 JTs、98s)。這些牌有成順子或同花的潛力。</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>新手 可以 玩 中等 起手牌 中 小對子 例如 99 88 77 同花 a 如 a5s 同花 連張 如 jts 98s 牌 有 成 順子 或 同花 潛力</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>3</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>該直接丟掉的起手牌：不成對、又不同花、數字又差很多的雜牌，新手直接棄牌就好，不要因為想玩而勉強進場。</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>該 直接 丟掉 起手牌 不成 又 不同 花 數字 又 差 很多 雜牌 新手 直接 棄牌 好 不要 因為 想 玩 勉強 進場</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>1</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>位置會大幅影響起手牌選擇：在前面位置(如槍口位 UTG)後面還有很多人沒行動，只玩很強的牌；在後面位置(如按鈕位 BTN)可以玩寬一點。口訣是「位置越好，能玩的牌越多」。</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>位置 大幅 影響 起手牌 選擇 前面 位置 如 槍口位 utg 後 面 還有 很多 人 沒 行動 只 玩 很強 牌 在後面 位置 如 按鈕位 btn 可以 玩 寬 一點 口訣 位置 越 好 能 玩 牌 越 多</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>0</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>同花不代表什麼牌都能玩。雖然同花的兩張牌比不同花稍強一點點，但像 92 同花這種差距太大的牌還是該丟，別被「同花」兩個字騙了。</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>同花 不 代表 什麼 牌 能 玩 雖然 同花 兩 張牌 比 不同 花 稍強 一點點 但 像 92 同花 這種 差距 太大 牌 還是 該 丟 別 同花 兩個 字 騙</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>4</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>該不該 limp(只跟大盲、不加注就進場)？新手通常不建議 limp，因為放棄了主動權、也容易讓很多人一起看翻牌。要玩這手牌就用加注進場，不想玩就棄牌。</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>該 不 該 limp 只 跟 大盲 不 加注 進場 ？ 新手 通常 不建議 limp 因為 放棄 主動權 容易 讓 很多 人 一起 看 翻牌 要 玩 這手牌 用 加注 進場 不想 玩 棄牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>1</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>人少的牌桌(例如 6 人桌)起手牌可以比 9 人滿桌玩得更寬，因為位置輪轉快、盲注壓力大；滿桌則要打得更緊一些。</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>人少 牌桌 例如 6 人桌 起手牌 可以 比 9 人滿 桌玩得 更 寬 因為 位置 輪 轉快 盲注 壓力 大 滿桌則 要 打 得 更 緊 一些</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>3</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>最常見的新手錯誤是「玩太多手牌」。覺得每手都想參與，結果常拿著弱牌進場、翻牌後陷入兩難。正確做法是打緊一點，多數爛牌直接棄掉。</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>最常見 新手 錯誤 玩太多 手牌 覺得 每手 想 參 結果 常拿著 弱牌 進場 翻牌後 陷入 兩難 正確 做法 打緊 一點 多數爛牌 直接 棄掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>4</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>新手很愛 limp(只跟不加注)進場。這會放棄主動權、把底池搞得很多人一起玩。建議：值得玩的牌就用加注進場，不值得就棄牌，少用 limp。</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>新手 很 愛 limp 只 跟 不 加注 進場 這會 放棄 主動權 底池 搞 得 很多 人 一起 玩 建議 值得 玩 牌 用 加注 進場 不 值得 棄牌 少 用 limp</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>0</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>無腦跟注是燒錢的壞習慣：沒有明確理由就一直跟注到底。每次跟注前先問自己「我跟的理由是什麼」，要嘛有勝算或好賠率，要嘛就棄牌。</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>無腦 跟注 燒錢 壞 習慣 沒有 明確 理由 一直 跟注 到底 每次 跟注 前先問 自己 我 跟 理由 什麼 要 嘛 有 勝算 或 好 賠率 要 嘛 棄牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>0</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>追聽牌不算賠率：為了湊同花或順子一路跟注，卻沒算底池賠率划不划算。聽牌要看「補牌張數」和「底池給的賠率」是否值得追。</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>追聽牌 不算 賠率 湊 同花 或 順子 一路 跟注 卻 沒算 底池賠率 划 不划算 聽牌 要 看 補牌 張數 和 底池給 賠率 是否 值得 追</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>3</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>上頭(tilt)：輸了一手大牌之後情緒失控、開始亂打想討回來，結果輸更多。最好的處理方式是先離桌休息、冷靜下來，再決定要不要繼續。</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>上頭 tilt 輸 一手 大牌 之後情緒 失控 開始 亂 打 想 討 回來 結果 輸 更 多 最好 處理 方式 先離桌 休息 冷靜 下來 再 決定 要 不要 繼續</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>0</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>太黏成手牌：拿到一對 A 就死不放手，明明牌面出現同花或順子的危險、對手又重注，還是硬跟到底。學會在情況不對時放掉好牌，是進步的關鍵。</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>太 黏成 手牌 拿到 一對 a 死 不 放手 明明 牌面 出現 同花 或 順子 危險 對手 又 重注 還是 硬 跟 到底 學會 情況 不 時 放掉 好牌 進步 關鍵</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>1</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>不看位置就行動：忽略自己在這手牌是先行動還是後行動。位置差時要更謹慎，位置好(較晚行動)才有資訊優勢可以玩寬一點。</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>不看 位置 行動 忽略 自己 這手牌 先 行動 還是 後 行動 位置 差時 要 更 謹慎 位置 好 較晚 行動 才 有 資訊 優勢 可以 玩 寬 一點</t>
         </is>
       </c>
     </row>
